--- a/diseases/d165/2026-2029.xlsx
+++ b/diseases/d165/2026-2029.xlsx
@@ -23028,12 +23028,12 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Taiwan, China</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -23067,81 +23067,95 @@
         </is>
       </c>
       <c r="N118" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="O118" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="R118" t="n">
-        <v>0.04345692446436896</v>
+        <v>0.009344880428283346</v>
       </c>
       <c r="S118" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U118" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_ENTAMOEBA</t>
+        </is>
+      </c>
+      <c r="AA118" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO118" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP118" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR118" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS118" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ118" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS118" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_ENTAMOEBA</t>
+        </is>
+      </c>
       <c r="AT118" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU118" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV118" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ118" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA118" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB118" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC118" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -23168,17 +23182,17 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -23203,7 +23217,7 @@
       </c>
       <c r="L119" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M119" t="inlineStr">
@@ -23212,31 +23226,103 @@
         </is>
       </c>
       <c r="N119" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="O119" t="n">
-        <v>9</v>
-      </c>
-      <c r="P119" t="n">
-        <v>9</v>
-      </c>
-      <c r="R119" t="n">
-        <v>0.007351275668091897</v>
-      </c>
-      <c r="S119" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="U119" t="inlineStr">
         <is>
-          <t>SER_JP_AMEBIASIS_WEEKLY</t>
+          <t>SER_SE_FOHM_SMINET_ENTAMOEBA</t>
+        </is>
+      </c>
+      <c r="V119" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_ENTAMOEBA</t>
+        </is>
+      </c>
+      <c r="W119" t="inlineStr">
+        <is>
+          <t>SRC_SE_FOHM_SMINET</t>
+        </is>
+      </c>
+      <c r="X119" t="inlineStr">
+        <is>
+          <t>Entamoeba histolytica</t>
+        </is>
+      </c>
+      <c r="Y119" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z119" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
         <is>
-          <t>weekly</t>
-        </is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB119" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC119" t="inlineStr">
+        <is>
+          <t>country:SE:national</t>
+        </is>
+      </c>
+      <c r="AD119" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE119" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF119" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG119" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH119" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI119" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ119" t="inlineStr">
+        <is>
+          <t>SE_FOHM_SMINET_current</t>
+        </is>
+      </c>
+      <c r="AK119" t="inlineStr">
+        <is>
+          <t>Sweden FHM SmiNet national monthly notification series; FHM Entamoeba histolytica source category.</t>
+        </is>
+      </c>
+      <c r="AM119" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN119" t="b">
+        <v>1</v>
       </c>
       <c r="AO119" t="inlineStr">
         <is>
@@ -23255,7 +23341,7 @@
       </c>
       <c r="AS119" t="inlineStr">
         <is>
-          <t>SER_JP_AMEBIASIS_WEEKLY</t>
+          <t>SER_SE_FOHM_SMINET_ENTAMOEBA</t>
         </is>
       </c>
       <c r="AT119" t="n">
@@ -23268,42 +23354,42 @@
       </c>
       <c r="AV119" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW119" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY119" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ119" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA119" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB119" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC119" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -23330,17 +23416,17 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>TW</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Taiwan, China</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -23365,7 +23451,7 @@
       </c>
       <c r="L120" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M120" t="inlineStr">
@@ -23374,173 +23460,81 @@
         </is>
       </c>
       <c r="N120" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O120" t="n">
-        <v>9</v>
-      </c>
-      <c r="P120" t="n">
-        <v>9</v>
-      </c>
-      <c r="U120" t="inlineStr">
-        <is>
-          <t>SER_JP_AMEBIASIS_WEEKLY</t>
-        </is>
-      </c>
-      <c r="V120" t="inlineStr">
-        <is>
-          <t>SER_JP_AMEBIASIS_WEEKLY</t>
-        </is>
-      </c>
-      <c r="W120" t="inlineStr">
-        <is>
-          <t>SRC_JP_NIID</t>
-        </is>
-      </c>
-      <c r="X120" t="inlineStr">
-        <is>
-          <t>Amoebic dysentery</t>
-        </is>
-      </c>
-      <c r="Y120" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z120" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
-      <c r="AA120" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB120" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC120" t="inlineStr">
-        <is>
-          <t>country:JP:national</t>
-        </is>
-      </c>
-      <c r="AD120" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE120" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF120" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG120" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH120" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI120" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ120" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
-        </is>
-      </c>
-      <c r="AK120" t="inlineStr">
-        <is>
-          <t>Japan NIID amoebic dysentery notifications.</t>
-        </is>
-      </c>
-      <c r="AM120" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN120" t="b">
-        <v>1</v>
+        <v>10</v>
+      </c>
+      <c r="R120" t="n">
+        <v>0.04345692446436896</v>
+      </c>
+      <c r="S120" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO120" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP120" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ120" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS120" t="inlineStr">
-        <is>
-          <t>SER_JP_AMEBIASIS_WEEKLY</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR120" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS120" t="inlineStr"/>
       <c r="AT120" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU120" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV120" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="AW120" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="AY120" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ120" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="BA120" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="BB120" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="BC120" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -23602,7 +23596,7 @@
       </c>
       <c r="L121" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M121" t="inlineStr">
@@ -23611,16 +23605,16 @@
         </is>
       </c>
       <c r="N121" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="O121" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="P121" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="R121" t="n">
-        <v>0.00653446726052613</v>
+        <v>0.007351275668091897</v>
       </c>
       <c r="S121" t="inlineStr">
         <is>
@@ -23764,7 +23758,7 @@
       </c>
       <c r="L122" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M122" t="inlineStr">
@@ -23773,13 +23767,13 @@
         </is>
       </c>
       <c r="N122" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="O122" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="P122" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U122" t="inlineStr">
         <is>
@@ -24001,7 +23995,7 @@
       </c>
       <c r="L123" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="M123" t="inlineStr">
@@ -24010,16 +24004,16 @@
         </is>
       </c>
       <c r="N123" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="O123" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="P123" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="R123" t="n">
-        <v>0.001633616815131532</v>
+        <v>0.00653446726052613</v>
       </c>
       <c r="S123" t="inlineStr">
         <is>
@@ -24163,7 +24157,7 @@
       </c>
       <c r="L124" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="M124" t="inlineStr">
@@ -24172,13 +24166,13 @@
         </is>
       </c>
       <c r="N124" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="O124" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="P124" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="U124" t="inlineStr">
         <is>
@@ -24400,7 +24394,7 @@
       </c>
       <c r="L125" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="M125" t="inlineStr">
@@ -24409,16 +24403,16 @@
         </is>
       </c>
       <c r="N125" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="O125" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="P125" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="R125" t="n">
-        <v>0.00898489248322343</v>
+        <v>0.001633616815131532</v>
       </c>
       <c r="S125" t="inlineStr">
         <is>
@@ -24562,7 +24556,7 @@
       </c>
       <c r="L126" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="M126" t="inlineStr">
@@ -24571,13 +24565,13 @@
         </is>
       </c>
       <c r="N126" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="O126" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="P126" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="U126" t="inlineStr">
         <is>
@@ -24769,12 +24763,12 @@
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
@@ -24799,22 +24793,25 @@
       </c>
       <c r="L127" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="M127" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N127" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="O127" t="n">
-        <v>0</v>
+        <v>11</v>
+      </c>
+      <c r="P127" t="n">
+        <v>11</v>
       </c>
       <c r="R127" t="n">
-        <v>0</v>
+        <v>0.00898489248322343</v>
       </c>
       <c r="S127" t="inlineStr">
         <is>
@@ -24823,12 +24820,12 @@
       </c>
       <c r="U127" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1290</t>
+          <t>SER_JP_AMEBIASIS_WEEKLY</t>
         </is>
       </c>
       <c r="AA127" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO127" t="inlineStr">
@@ -24843,12 +24840,12 @@
       </c>
       <c r="AQ127" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS127" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1290</t>
+          <t>SER_JP_AMEBIASIS_WEEKLY</t>
         </is>
       </c>
       <c r="AT127" t="n">
@@ -24856,47 +24853,47 @@
       </c>
       <c r="AU127" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV127" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW127" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX127" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY127" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ127" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA127" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB127" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC127" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -24928,12 +24925,12 @@
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
@@ -24958,38 +24955,41 @@
       </c>
       <c r="L128" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="M128" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N128" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="O128" t="n">
-        <v>0</v>
+        <v>11</v>
+      </c>
+      <c r="P128" t="n">
+        <v>11</v>
       </c>
       <c r="U128" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1290</t>
+          <t>SER_JP_AMEBIASIS_WEEKLY</t>
         </is>
       </c>
       <c r="V128" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1290</t>
+          <t>SER_JP_AMEBIASIS_WEEKLY</t>
         </is>
       </c>
       <c r="W128" t="inlineStr">
         <is>
-          <t>SRC_FI_THL_TTR</t>
+          <t>SRC_JP_NIID</t>
         </is>
       </c>
       <c r="X128" t="inlineStr">
         <is>
-          <t>Amebiasis</t>
+          <t>Amoebic dysentery</t>
         </is>
       </c>
       <c r="Y128" t="inlineStr">
@@ -24999,12 +24999,12 @@
       </c>
       <c r="Z128" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA128" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AB128" t="inlineStr">
@@ -25014,7 +25014,7 @@
       </c>
       <c r="AC128" t="inlineStr">
         <is>
-          <t>country:FI:national</t>
+          <t>country:JP:national</t>
         </is>
       </c>
       <c r="AD128" t="inlineStr">
@@ -25029,7 +25029,7 @@
       </c>
       <c r="AF128" t="inlineStr">
         <is>
-          <t>conditional</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="AG128" t="inlineStr">
@@ -25049,12 +25049,12 @@
       </c>
       <c r="AJ128" t="inlineStr">
         <is>
-          <t>FI_THL_TTR_reporting_group</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK128" t="inlineStr">
         <is>
-          <t>Finland THL national monthly notification series; THL reporting group code 1290.</t>
+          <t>Japan NIID amoebic dysentery notifications.</t>
         </is>
       </c>
       <c r="AM128" t="inlineStr">
@@ -25077,12 +25077,12 @@
       </c>
       <c r="AQ128" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS128" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1290</t>
+          <t>SER_JP_AMEBIASIS_WEEKLY</t>
         </is>
       </c>
       <c r="AT128" t="n">
@@ -25090,45 +25090,438 @@
       </c>
       <c r="AU128" t="inlineStr">
         <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV128" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW128" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX128" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY128" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ128" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA128" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB128" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC128" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>D165</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>amebiasis</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>Amebiasis</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>FI</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>D165</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>Amebiasis</t>
+        </is>
+      </c>
+      <c r="J129" t="inlineStr">
+        <is>
+          <t>阿米巴病</t>
+        </is>
+      </c>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L129" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M129" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N129" t="n">
+        <v>0</v>
+      </c>
+      <c r="O129" t="n">
+        <v>0</v>
+      </c>
+      <c r="R129" t="n">
+        <v>0</v>
+      </c>
+      <c r="S129" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U129" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1290</t>
+        </is>
+      </c>
+      <c r="AA129" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO129" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP129" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ129" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AS129" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1290</t>
+        </is>
+      </c>
+      <c r="AT129" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU129" t="inlineStr">
+        <is>
           <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
-      <c r="AV128" t="inlineStr">
+      <c r="AV129" t="inlineStr">
         <is>
           <t>thl_ttr</t>
         </is>
       </c>
-      <c r="AW128" t="inlineStr">
+      <c r="AW129" t="inlineStr">
         <is>
           <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
-      <c r="AX128" t="inlineStr">
+      <c r="AX129" t="inlineStr">
         <is>
           <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
-      <c r="AY128" t="inlineStr">
+      <c r="AY129" t="inlineStr">
         <is>
           <t>cube_csv</t>
         </is>
       </c>
-      <c r="AZ128" t="inlineStr">
+      <c r="AZ129" t="inlineStr">
         <is>
           <t>thl_ttr</t>
         </is>
       </c>
-      <c r="BA128" t="inlineStr">
+      <c r="BA129" t="inlineStr">
         <is>
           <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
-      <c r="BB128" t="inlineStr">
+      <c r="BB129" t="inlineStr">
         <is>
           <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
-      <c r="BC128" t="inlineStr">
+      <c r="BC129" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>D165</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>amebiasis</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>Amebiasis</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>FI</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>D165</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>Amebiasis</t>
+        </is>
+      </c>
+      <c r="J130" t="inlineStr">
+        <is>
+          <t>阿米巴病</t>
+        </is>
+      </c>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L130" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M130" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N130" t="n">
+        <v>0</v>
+      </c>
+      <c r="O130" t="n">
+        <v>0</v>
+      </c>
+      <c r="U130" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1290</t>
+        </is>
+      </c>
+      <c r="V130" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1290</t>
+        </is>
+      </c>
+      <c r="W130" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X130" t="inlineStr">
+        <is>
+          <t>Amebiasis</t>
+        </is>
+      </c>
+      <c r="Y130" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z130" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA130" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB130" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC130" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD130" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE130" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF130" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG130" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH130" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI130" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ130" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK130" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; THL reporting group code 1290.</t>
+        </is>
+      </c>
+      <c r="AM130" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN130" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO130" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP130" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ130" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AS130" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1290</t>
+        </is>
+      </c>
+      <c r="AT130" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU130" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
+      </c>
+      <c r="AV130" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="AW130" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="AX130" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="AY130" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+      <c r="AZ130" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="BA130" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="BB130" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="BC130" t="inlineStr">
         <is>
           <t>cube_csv</t>
         </is>
@@ -25250,7 +25643,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="10">
@@ -25260,7 +25653,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="11">
@@ -25280,7 +25673,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="13">
@@ -25312,7 +25705,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>512</v>
+        <v>513</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d165/2026-2029.xlsx
+++ b/diseases/d165/2026-2029.xlsx
@@ -25162,12 +25162,12 @@
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
@@ -25192,22 +25192,25 @@
       </c>
       <c r="L129" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="M129" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N129" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O129" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="P129" t="n">
+        <v>1</v>
       </c>
       <c r="R129" t="n">
-        <v>0</v>
+        <v>0.0008168084075657662</v>
       </c>
       <c r="S129" t="inlineStr">
         <is>
@@ -25216,12 +25219,12 @@
       </c>
       <c r="U129" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1290</t>
+          <t>SER_JP_AMEBIASIS_WEEKLY</t>
         </is>
       </c>
       <c r="AA129" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO129" t="inlineStr">
@@ -25236,12 +25239,12 @@
       </c>
       <c r="AQ129" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS129" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1290</t>
+          <t>SER_JP_AMEBIASIS_WEEKLY</t>
         </is>
       </c>
       <c r="AT129" t="n">
@@ -25249,47 +25252,47 @@
       </c>
       <c r="AU129" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV129" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW129" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX129" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY129" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ129" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA129" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB129" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC129" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -25321,12 +25324,12 @@
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
@@ -25351,38 +25354,41 @@
       </c>
       <c r="L130" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="M130" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N130" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O130" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="P130" t="n">
+        <v>1</v>
       </c>
       <c r="U130" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1290</t>
+          <t>SER_JP_AMEBIASIS_WEEKLY</t>
         </is>
       </c>
       <c r="V130" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1290</t>
+          <t>SER_JP_AMEBIASIS_WEEKLY</t>
         </is>
       </c>
       <c r="W130" t="inlineStr">
         <is>
-          <t>SRC_FI_THL_TTR</t>
+          <t>SRC_JP_NIID</t>
         </is>
       </c>
       <c r="X130" t="inlineStr">
         <is>
-          <t>Amebiasis</t>
+          <t>Amoebic dysentery</t>
         </is>
       </c>
       <c r="Y130" t="inlineStr">
@@ -25392,12 +25398,12 @@
       </c>
       <c r="Z130" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA130" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AB130" t="inlineStr">
@@ -25407,7 +25413,7 @@
       </c>
       <c r="AC130" t="inlineStr">
         <is>
-          <t>country:FI:national</t>
+          <t>country:JP:national</t>
         </is>
       </c>
       <c r="AD130" t="inlineStr">
@@ -25422,7 +25428,7 @@
       </c>
       <c r="AF130" t="inlineStr">
         <is>
-          <t>conditional</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="AG130" t="inlineStr">
@@ -25442,12 +25448,12 @@
       </c>
       <c r="AJ130" t="inlineStr">
         <is>
-          <t>FI_THL_TTR_reporting_group</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK130" t="inlineStr">
         <is>
-          <t>Finland THL national monthly notification series; THL reporting group code 1290.</t>
+          <t>Japan NIID amoebic dysentery notifications.</t>
         </is>
       </c>
       <c r="AM130" t="inlineStr">
@@ -25470,12 +25476,12 @@
       </c>
       <c r="AQ130" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS130" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1290</t>
+          <t>SER_JP_AMEBIASIS_WEEKLY</t>
         </is>
       </c>
       <c r="AT130" t="n">
@@ -25483,45 +25489,438 @@
       </c>
       <c r="AU130" t="inlineStr">
         <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV130" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW130" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX130" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY130" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ130" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA130" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB130" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC130" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>D165</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>amebiasis</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>Amebiasis</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>FI</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>D165</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>Amebiasis</t>
+        </is>
+      </c>
+      <c r="J131" t="inlineStr">
+        <is>
+          <t>阿米巴病</t>
+        </is>
+      </c>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L131" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M131" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N131" t="n">
+        <v>0</v>
+      </c>
+      <c r="O131" t="n">
+        <v>0</v>
+      </c>
+      <c r="R131" t="n">
+        <v>0</v>
+      </c>
+      <c r="S131" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U131" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1290</t>
+        </is>
+      </c>
+      <c r="AA131" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO131" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP131" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ131" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AS131" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1290</t>
+        </is>
+      </c>
+      <c r="AT131" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU131" t="inlineStr">
+        <is>
           <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
-      <c r="AV130" t="inlineStr">
+      <c r="AV131" t="inlineStr">
         <is>
           <t>thl_ttr</t>
         </is>
       </c>
-      <c r="AW130" t="inlineStr">
+      <c r="AW131" t="inlineStr">
         <is>
           <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
-      <c r="AX130" t="inlineStr">
+      <c r="AX131" t="inlineStr">
         <is>
           <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
-      <c r="AY130" t="inlineStr">
+      <c r="AY131" t="inlineStr">
         <is>
           <t>cube_csv</t>
         </is>
       </c>
-      <c r="AZ130" t="inlineStr">
+      <c r="AZ131" t="inlineStr">
         <is>
           <t>thl_ttr</t>
         </is>
       </c>
-      <c r="BA130" t="inlineStr">
+      <c r="BA131" t="inlineStr">
         <is>
           <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
-      <c r="BB130" t="inlineStr">
+      <c r="BB131" t="inlineStr">
         <is>
           <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
-      <c r="BC130" t="inlineStr">
+      <c r="BC131" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>D165</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>amebiasis</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>Amebiasis</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>FI</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>D165</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>Amebiasis</t>
+        </is>
+      </c>
+      <c r="J132" t="inlineStr">
+        <is>
+          <t>阿米巴病</t>
+        </is>
+      </c>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L132" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M132" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N132" t="n">
+        <v>0</v>
+      </c>
+      <c r="O132" t="n">
+        <v>0</v>
+      </c>
+      <c r="U132" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1290</t>
+        </is>
+      </c>
+      <c r="V132" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1290</t>
+        </is>
+      </c>
+      <c r="W132" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X132" t="inlineStr">
+        <is>
+          <t>Amebiasis</t>
+        </is>
+      </c>
+      <c r="Y132" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z132" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA132" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB132" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC132" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD132" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE132" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF132" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG132" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH132" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI132" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ132" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK132" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; THL reporting group code 1290.</t>
+        </is>
+      </c>
+      <c r="AM132" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN132" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO132" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP132" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ132" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AS132" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1290</t>
+        </is>
+      </c>
+      <c r="AT132" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU132" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
+      </c>
+      <c r="AV132" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="AW132" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="AX132" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="AY132" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+      <c r="AZ132" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="BA132" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="BB132" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="BC132" t="inlineStr">
         <is>
           <t>cube_csv</t>
         </is>
@@ -25643,7 +26042,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="10">
@@ -25653,7 +26052,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>129</v>
+        <v>131</v>
       </c>
     </row>
     <row r="11">
@@ -25673,7 +26072,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="13">
@@ -25705,7 +26104,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>513</v>
+        <v>514</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d165/2026-2029.xlsx
+++ b/diseases/d165/2026-2029.xlsx
@@ -6911,10 +6911,10 @@
         </is>
       </c>
       <c r="N34" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="O34" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="S34" t="inlineStr">
         <is>
@@ -7067,10 +7067,10 @@
         </is>
       </c>
       <c r="N35" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="O35" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U35" t="inlineStr">
         <is>
@@ -16940,10 +16940,10 @@
         </is>
       </c>
       <c r="N86" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O86" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="S86" t="inlineStr">
         <is>
@@ -17096,10 +17096,10 @@
         </is>
       </c>
       <c r="N87" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O87" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U87" t="inlineStr">
         <is>
@@ -19963,12 +19963,12 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>CA-ON</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Ontario, Canada</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -20002,22 +20002,19 @@
         </is>
       </c>
       <c r="N102" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="O102" t="n">
-        <v>0</v>
-      </c>
-      <c r="R102" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="S102" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>missing_population</t>
         </is>
       </c>
       <c r="U102" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1290</t>
+          <t>SER_CA_ON_PHO_IDTO_AMEBIASIS_MONTHLY</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -20037,12 +20034,12 @@
       </c>
       <c r="AQ102" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS102" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1290</t>
+          <t>SER_CA_ON_PHO_IDTO_AMEBIASIS_MONTHLY</t>
         </is>
       </c>
       <c r="AT102" t="n">
@@ -20050,47 +20047,47 @@
       </c>
       <c r="AU102" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV102" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ102" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="BA102" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="BB102" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="BC102" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -20122,12 +20119,12 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>CA-ON</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Ontario, Canada</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -20161,24 +20158,24 @@
         </is>
       </c>
       <c r="N103" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="O103" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="U103" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1290</t>
+          <t>SER_CA_ON_PHO_IDTO_AMEBIASIS_MONTHLY</t>
         </is>
       </c>
       <c r="V103" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1290</t>
+          <t>SER_CA_ON_PHO_IDTO_AMEBIASIS_MONTHLY</t>
         </is>
       </c>
       <c r="W103" t="inlineStr">
         <is>
-          <t>SRC_FI_THL_TTR</t>
+          <t>SRC_CA_ON_PHO_IDTO</t>
         </is>
       </c>
       <c r="X103" t="inlineStr">
@@ -20193,7 +20190,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -20208,7 +20205,7 @@
       </c>
       <c r="AC103" t="inlineStr">
         <is>
-          <t>country:FI:national</t>
+          <t>country:CA-ON:national</t>
         </is>
       </c>
       <c r="AD103" t="inlineStr">
@@ -20243,17 +20240,17 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>FI_THL_TTR_reporting_group</t>
+          <t>PHO_IDTO_2026_07</t>
         </is>
       </c>
       <c r="AK103" t="inlineStr">
         <is>
-          <t>Finland THL national monthly notification series; THL reporting group code 1290.</t>
+          <t>PHO IDTO current-year monthly preliminary amebiasis notifications; confirmed cases only under the July 2026 technical notes.</t>
         </is>
       </c>
       <c r="AM103" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>provisional</t>
         </is>
       </c>
       <c r="AN103" t="b">
@@ -20271,12 +20268,12 @@
       </c>
       <c r="AQ103" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS103" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1290</t>
+          <t>SER_CA_ON_PHO_IDTO_AMEBIASIS_MONTHLY</t>
         </is>
       </c>
       <c r="AT103" t="n">
@@ -20284,47 +20281,47 @@
       </c>
       <c r="AU103" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV103" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ103" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="BA103" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="BB103" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="BC103" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -20356,12 +20353,12 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -20395,81 +20392,95 @@
         </is>
       </c>
       <c r="N104" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O104" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R104" t="n">
-        <v>0.02710540560393419</v>
+        <v>0</v>
       </c>
       <c r="S104" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U104" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1290</t>
+        </is>
+      </c>
+      <c r="AA104" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO104" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP104" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR104" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS104" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ104" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AS104" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1290</t>
+        </is>
+      </c>
       <c r="AT104" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU104" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV104" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ104" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA104" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB104" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC104" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -20496,17 +20507,17 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -20540,22 +20551,39 @@
         </is>
       </c>
       <c r="N105" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O105" t="n">
-        <v>5</v>
-      </c>
-      <c r="R105" t="n">
-        <v>0.04672440214141673</v>
-      </c>
-      <c r="S105" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>0</v>
       </c>
       <c r="U105" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_ENTAMOEBA</t>
+          <t>SER_FI_THL_TTR_1290</t>
+        </is>
+      </c>
+      <c r="V105" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1290</t>
+        </is>
+      </c>
+      <c r="W105" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X105" t="inlineStr">
+        <is>
+          <t>Amebiasis</t>
+        </is>
+      </c>
+      <c r="Y105" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z105" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -20563,6 +20591,64 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB105" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC105" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD105" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE105" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF105" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG105" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH105" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI105" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ105" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK105" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; THL reporting group code 1290.</t>
+        </is>
+      </c>
+      <c r="AM105" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN105" t="b">
+        <v>1</v>
+      </c>
       <c r="AO105" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -20575,12 +20661,12 @@
       </c>
       <c r="AQ105" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AS105" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_ENTAMOEBA</t>
+          <t>SER_FI_THL_TTR_1290</t>
         </is>
       </c>
       <c r="AT105" t="n">
@@ -20588,47 +20674,47 @@
       </c>
       <c r="AU105" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV105" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ105" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA105" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB105" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC105" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -20655,17 +20741,17 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -20699,170 +20785,81 @@
         </is>
       </c>
       <c r="N106" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="O106" t="n">
-        <v>5</v>
-      </c>
-      <c r="U106" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_ENTAMOEBA</t>
-        </is>
-      </c>
-      <c r="V106" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_ENTAMOEBA</t>
-        </is>
-      </c>
-      <c r="W106" t="inlineStr">
-        <is>
-          <t>SRC_SE_FOHM_SMINET</t>
-        </is>
-      </c>
-      <c r="X106" t="inlineStr">
-        <is>
-          <t>Entamoeba histolytica</t>
-        </is>
-      </c>
-      <c r="Y106" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z106" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
-      <c r="AA106" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB106" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC106" t="inlineStr">
-        <is>
-          <t>country:SE:national</t>
-        </is>
-      </c>
-      <c r="AD106" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE106" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF106" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG106" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH106" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI106" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ106" t="inlineStr">
-        <is>
-          <t>SE_FOHM_SMINET_current</t>
-        </is>
-      </c>
-      <c r="AK106" t="inlineStr">
-        <is>
-          <t>Sweden FHM SmiNet national monthly notification series; FHM Entamoeba histolytica source category.</t>
-        </is>
-      </c>
-      <c r="AM106" t="inlineStr">
-        <is>
-          <t>revised</t>
-        </is>
-      </c>
-      <c r="AN106" t="b">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="R106" t="n">
+        <v>0.02710540560393419</v>
+      </c>
+      <c r="S106" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO106" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP106" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ106" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS106" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_ENTAMOEBA</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR106" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS106" t="inlineStr"/>
       <c r="AT106" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU106" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV106" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ106" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA106" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB106" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC106" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -20894,12 +20891,12 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Taiwan, China</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -20933,81 +20930,95 @@
         </is>
       </c>
       <c r="N107" t="n">
-        <v>33</v>
+        <v>5</v>
       </c>
       <c r="O107" t="n">
-        <v>33</v>
+        <v>5</v>
       </c>
       <c r="R107" t="n">
-        <v>0.1434078507324176</v>
+        <v>0.04672440214141673</v>
       </c>
       <c r="S107" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U107" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_ENTAMOEBA</t>
+        </is>
+      </c>
+      <c r="AA107" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO107" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP107" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR107" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS107" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ107" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS107" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_ENTAMOEBA</t>
+        </is>
+      </c>
       <c r="AT107" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU107" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV107" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ107" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA107" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB107" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC107" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -21034,17 +21045,17 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -21069,7 +21080,7 @@
       </c>
       <c r="L108" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M108" t="inlineStr">
@@ -21078,31 +21089,103 @@
         </is>
       </c>
       <c r="N108" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O108" t="n">
-        <v>4</v>
-      </c>
-      <c r="P108" t="n">
-        <v>4</v>
-      </c>
-      <c r="R108" t="n">
-        <v>0.003267233630263065</v>
-      </c>
-      <c r="S108" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>5</v>
       </c>
       <c r="U108" t="inlineStr">
         <is>
-          <t>SER_JP_AMEBIASIS_WEEKLY</t>
+          <t>SER_SE_FOHM_SMINET_ENTAMOEBA</t>
+        </is>
+      </c>
+      <c r="V108" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_ENTAMOEBA</t>
+        </is>
+      </c>
+      <c r="W108" t="inlineStr">
+        <is>
+          <t>SRC_SE_FOHM_SMINET</t>
+        </is>
+      </c>
+      <c r="X108" t="inlineStr">
+        <is>
+          <t>Entamoeba histolytica</t>
+        </is>
+      </c>
+      <c r="Y108" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z108" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
         <is>
-          <t>weekly</t>
-        </is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB108" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC108" t="inlineStr">
+        <is>
+          <t>country:SE:national</t>
+        </is>
+      </c>
+      <c r="AD108" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE108" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF108" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG108" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH108" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI108" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ108" t="inlineStr">
+        <is>
+          <t>SE_FOHM_SMINET_current</t>
+        </is>
+      </c>
+      <c r="AK108" t="inlineStr">
+        <is>
+          <t>Sweden FHM SmiNet national monthly notification series; FHM Entamoeba histolytica source category.</t>
+        </is>
+      </c>
+      <c r="AM108" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN108" t="b">
+        <v>1</v>
       </c>
       <c r="AO108" t="inlineStr">
         <is>
@@ -21121,7 +21204,7 @@
       </c>
       <c r="AS108" t="inlineStr">
         <is>
-          <t>SER_JP_AMEBIASIS_WEEKLY</t>
+          <t>SER_SE_FOHM_SMINET_ENTAMOEBA</t>
         </is>
       </c>
       <c r="AT108" t="n">
@@ -21134,42 +21217,42 @@
       </c>
       <c r="AV108" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ108" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA108" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB108" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC108" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -21196,17 +21279,17 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>TW</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Taiwan, China</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -21231,7 +21314,7 @@
       </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M109" t="inlineStr">
@@ -21240,173 +21323,81 @@
         </is>
       </c>
       <c r="N109" t="n">
-        <v>4</v>
+        <v>33</v>
       </c>
       <c r="O109" t="n">
-        <v>4</v>
-      </c>
-      <c r="P109" t="n">
-        <v>4</v>
-      </c>
-      <c r="U109" t="inlineStr">
-        <is>
-          <t>SER_JP_AMEBIASIS_WEEKLY</t>
-        </is>
-      </c>
-      <c r="V109" t="inlineStr">
-        <is>
-          <t>SER_JP_AMEBIASIS_WEEKLY</t>
-        </is>
-      </c>
-      <c r="W109" t="inlineStr">
-        <is>
-          <t>SRC_JP_NIID</t>
-        </is>
-      </c>
-      <c r="X109" t="inlineStr">
-        <is>
-          <t>Amoebic dysentery</t>
-        </is>
-      </c>
-      <c r="Y109" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z109" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
-      <c r="AA109" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB109" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC109" t="inlineStr">
-        <is>
-          <t>country:JP:national</t>
-        </is>
-      </c>
-      <c r="AD109" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE109" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF109" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG109" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH109" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI109" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ109" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
-        </is>
-      </c>
-      <c r="AK109" t="inlineStr">
-        <is>
-          <t>Japan NIID amoebic dysentery notifications.</t>
-        </is>
-      </c>
-      <c r="AM109" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN109" t="b">
-        <v>1</v>
+        <v>33</v>
+      </c>
+      <c r="R109" t="n">
+        <v>0.1434078507324176</v>
+      </c>
+      <c r="S109" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO109" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP109" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ109" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS109" t="inlineStr">
-        <is>
-          <t>SER_JP_AMEBIASIS_WEEKLY</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR109" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS109" t="inlineStr"/>
       <c r="AT109" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU109" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV109" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ109" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="BA109" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="BB109" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="BC109" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -21468,7 +21459,7 @@
       </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="M110" t="inlineStr">
@@ -21477,16 +21468,16 @@
         </is>
       </c>
       <c r="N110" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="O110" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="P110" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="R110" t="n">
-        <v>0.005717658852960364</v>
+        <v>0.003267233630263065</v>
       </c>
       <c r="S110" t="inlineStr">
         <is>
@@ -21630,7 +21621,7 @@
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="M111" t="inlineStr">
@@ -21639,13 +21630,13 @@
         </is>
       </c>
       <c r="N111" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="O111" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="P111" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="U111" t="inlineStr">
         <is>
@@ -21867,7 +21858,7 @@
       </c>
       <c r="L112" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="M112" t="inlineStr">
@@ -21876,16 +21867,16 @@
         </is>
       </c>
       <c r="N112" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="O112" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="P112" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="R112" t="n">
-        <v>0.003267233630263065</v>
+        <v>0.005717658852960364</v>
       </c>
       <c r="S112" t="inlineStr">
         <is>
@@ -22029,7 +22020,7 @@
       </c>
       <c r="L113" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="M113" t="inlineStr">
@@ -22038,13 +22029,13 @@
         </is>
       </c>
       <c r="N113" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="O113" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="P113" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="U113" t="inlineStr">
         <is>
@@ -22266,7 +22257,7 @@
       </c>
       <c r="L114" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="M114" t="inlineStr">
@@ -22428,7 +22419,7 @@
       </c>
       <c r="L115" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="M115" t="inlineStr">
@@ -22635,12 +22626,12 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -22665,22 +22656,25 @@
       </c>
       <c r="L116" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="M116" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N116" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="O116" t="n">
-        <v>1</v>
+        <v>4</v>
+      </c>
+      <c r="P116" t="n">
+        <v>4</v>
       </c>
       <c r="R116" t="n">
-        <v>0.01778809170864137</v>
+        <v>0.003267233630263065</v>
       </c>
       <c r="S116" t="inlineStr">
         <is>
@@ -22689,12 +22683,12 @@
       </c>
       <c r="U116" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1290</t>
+          <t>SER_JP_AMEBIASIS_WEEKLY</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO116" t="inlineStr">
@@ -22709,12 +22703,12 @@
       </c>
       <c r="AQ116" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS116" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1290</t>
+          <t>SER_JP_AMEBIASIS_WEEKLY</t>
         </is>
       </c>
       <c r="AT116" t="n">
@@ -22722,47 +22716,47 @@
       </c>
       <c r="AU116" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV116" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ116" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA116" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB116" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC116" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -22794,12 +22788,12 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -22824,38 +22818,41 @@
       </c>
       <c r="L117" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="M117" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N117" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="O117" t="n">
-        <v>1</v>
+        <v>4</v>
+      </c>
+      <c r="P117" t="n">
+        <v>4</v>
       </c>
       <c r="U117" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1290</t>
+          <t>SER_JP_AMEBIASIS_WEEKLY</t>
         </is>
       </c>
       <c r="V117" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1290</t>
+          <t>SER_JP_AMEBIASIS_WEEKLY</t>
         </is>
       </c>
       <c r="W117" t="inlineStr">
         <is>
-          <t>SRC_FI_THL_TTR</t>
+          <t>SRC_JP_NIID</t>
         </is>
       </c>
       <c r="X117" t="inlineStr">
         <is>
-          <t>Amebiasis</t>
+          <t>Amoebic dysentery</t>
         </is>
       </c>
       <c r="Y117" t="inlineStr">
@@ -22865,12 +22862,12 @@
       </c>
       <c r="Z117" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AB117" t="inlineStr">
@@ -22880,7 +22877,7 @@
       </c>
       <c r="AC117" t="inlineStr">
         <is>
-          <t>country:FI:national</t>
+          <t>country:JP:national</t>
         </is>
       </c>
       <c r="AD117" t="inlineStr">
@@ -22895,7 +22892,7 @@
       </c>
       <c r="AF117" t="inlineStr">
         <is>
-          <t>conditional</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="AG117" t="inlineStr">
@@ -22915,12 +22912,12 @@
       </c>
       <c r="AJ117" t="inlineStr">
         <is>
-          <t>FI_THL_TTR_reporting_group</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK117" t="inlineStr">
         <is>
-          <t>Finland THL national monthly notification series; THL reporting group code 1290.</t>
+          <t>Japan NIID amoebic dysentery notifications.</t>
         </is>
       </c>
       <c r="AM117" t="inlineStr">
@@ -22943,12 +22940,12 @@
       </c>
       <c r="AQ117" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS117" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1290</t>
+          <t>SER_JP_AMEBIASIS_WEEKLY</t>
         </is>
       </c>
       <c r="AT117" t="n">
@@ -22956,47 +22953,47 @@
       </c>
       <c r="AU117" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV117" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ117" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA117" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB117" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC117" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -23028,12 +23025,12 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -23073,7 +23070,7 @@
         <v>1</v>
       </c>
       <c r="R118" t="n">
-        <v>0.009344880428283346</v>
+        <v>0.01778809170864137</v>
       </c>
       <c r="S118" t="inlineStr">
         <is>
@@ -23082,7 +23079,7 @@
       </c>
       <c r="U118" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_ENTAMOEBA</t>
+          <t>SER_FI_THL_TTR_1290</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
@@ -23102,12 +23099,12 @@
       </c>
       <c r="AQ118" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AS118" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_ENTAMOEBA</t>
+          <t>SER_FI_THL_TTR_1290</t>
         </is>
       </c>
       <c r="AT118" t="n">
@@ -23115,47 +23112,47 @@
       </c>
       <c r="AU118" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV118" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ118" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA118" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB118" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC118" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -23187,12 +23184,12 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -23233,22 +23230,22 @@
       </c>
       <c r="U119" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_ENTAMOEBA</t>
+          <t>SER_FI_THL_TTR_1290</t>
         </is>
       </c>
       <c r="V119" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_ENTAMOEBA</t>
+          <t>SER_FI_THL_TTR_1290</t>
         </is>
       </c>
       <c r="W119" t="inlineStr">
         <is>
-          <t>SRC_SE_FOHM_SMINET</t>
+          <t>SRC_FI_THL_TTR</t>
         </is>
       </c>
       <c r="X119" t="inlineStr">
         <is>
-          <t>Entamoeba histolytica</t>
+          <t>Amebiasis</t>
         </is>
       </c>
       <c r="Y119" t="inlineStr">
@@ -23273,7 +23270,7 @@
       </c>
       <c r="AC119" t="inlineStr">
         <is>
-          <t>country:SE:national</t>
+          <t>country:FI:national</t>
         </is>
       </c>
       <c r="AD119" t="inlineStr">
@@ -23308,17 +23305,17 @@
       </c>
       <c r="AJ119" t="inlineStr">
         <is>
-          <t>SE_FOHM_SMINET_current</t>
+          <t>FI_THL_TTR_reporting_group</t>
         </is>
       </c>
       <c r="AK119" t="inlineStr">
         <is>
-          <t>Sweden FHM SmiNet national monthly notification series; FHM Entamoeba histolytica source category.</t>
+          <t>Finland THL national monthly notification series; THL reporting group code 1290.</t>
         </is>
       </c>
       <c r="AM119" t="inlineStr">
         <is>
-          <t>revised</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN119" t="b">
@@ -23336,12 +23333,12 @@
       </c>
       <c r="AQ119" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AS119" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_ENTAMOEBA</t>
+          <t>SER_FI_THL_TTR_1290</t>
         </is>
       </c>
       <c r="AT119" t="n">
@@ -23349,47 +23346,47 @@
       </c>
       <c r="AU119" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV119" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW119" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY119" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ119" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA119" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB119" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC119" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -23421,12 +23418,12 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Taiwan, China</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -23460,81 +23457,95 @@
         </is>
       </c>
       <c r="N120" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="O120" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="R120" t="n">
-        <v>0.04345692446436896</v>
+        <v>0.009344880428283346</v>
       </c>
       <c r="S120" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U120" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_ENTAMOEBA</t>
+        </is>
+      </c>
+      <c r="AA120" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO120" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP120" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR120" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS120" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ120" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS120" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_ENTAMOEBA</t>
+        </is>
+      </c>
       <c r="AT120" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU120" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV120" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW120" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY120" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ120" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA120" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB120" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC120" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -23561,17 +23572,17 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -23596,7 +23607,7 @@
       </c>
       <c r="L121" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M121" t="inlineStr">
@@ -23605,31 +23616,103 @@
         </is>
       </c>
       <c r="N121" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="O121" t="n">
-        <v>9</v>
-      </c>
-      <c r="P121" t="n">
-        <v>9</v>
-      </c>
-      <c r="R121" t="n">
-        <v>0.007351275668091897</v>
-      </c>
-      <c r="S121" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="U121" t="inlineStr">
         <is>
-          <t>SER_JP_AMEBIASIS_WEEKLY</t>
+          <t>SER_SE_FOHM_SMINET_ENTAMOEBA</t>
+        </is>
+      </c>
+      <c r="V121" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_ENTAMOEBA</t>
+        </is>
+      </c>
+      <c r="W121" t="inlineStr">
+        <is>
+          <t>SRC_SE_FOHM_SMINET</t>
+        </is>
+      </c>
+      <c r="X121" t="inlineStr">
+        <is>
+          <t>Entamoeba histolytica</t>
+        </is>
+      </c>
+      <c r="Y121" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z121" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
         <is>
-          <t>weekly</t>
-        </is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB121" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC121" t="inlineStr">
+        <is>
+          <t>country:SE:national</t>
+        </is>
+      </c>
+      <c r="AD121" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE121" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF121" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG121" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH121" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI121" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ121" t="inlineStr">
+        <is>
+          <t>SE_FOHM_SMINET_current</t>
+        </is>
+      </c>
+      <c r="AK121" t="inlineStr">
+        <is>
+          <t>Sweden FHM SmiNet national monthly notification series; FHM Entamoeba histolytica source category.</t>
+        </is>
+      </c>
+      <c r="AM121" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN121" t="b">
+        <v>1</v>
       </c>
       <c r="AO121" t="inlineStr">
         <is>
@@ -23648,7 +23731,7 @@
       </c>
       <c r="AS121" t="inlineStr">
         <is>
-          <t>SER_JP_AMEBIASIS_WEEKLY</t>
+          <t>SER_SE_FOHM_SMINET_ENTAMOEBA</t>
         </is>
       </c>
       <c r="AT121" t="n">
@@ -23661,42 +23744,42 @@
       </c>
       <c r="AV121" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW121" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ121" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA121" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB121" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC121" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -23723,17 +23806,17 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>TW</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Taiwan, China</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
@@ -23758,7 +23841,7 @@
       </c>
       <c r="L122" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M122" t="inlineStr">
@@ -23767,173 +23850,81 @@
         </is>
       </c>
       <c r="N122" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O122" t="n">
-        <v>9</v>
-      </c>
-      <c r="P122" t="n">
-        <v>9</v>
-      </c>
-      <c r="U122" t="inlineStr">
-        <is>
-          <t>SER_JP_AMEBIASIS_WEEKLY</t>
-        </is>
-      </c>
-      <c r="V122" t="inlineStr">
-        <is>
-          <t>SER_JP_AMEBIASIS_WEEKLY</t>
-        </is>
-      </c>
-      <c r="W122" t="inlineStr">
-        <is>
-          <t>SRC_JP_NIID</t>
-        </is>
-      </c>
-      <c r="X122" t="inlineStr">
-        <is>
-          <t>Amoebic dysentery</t>
-        </is>
-      </c>
-      <c r="Y122" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z122" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
-      <c r="AA122" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB122" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC122" t="inlineStr">
-        <is>
-          <t>country:JP:national</t>
-        </is>
-      </c>
-      <c r="AD122" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE122" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF122" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG122" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH122" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI122" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ122" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
-        </is>
-      </c>
-      <c r="AK122" t="inlineStr">
-        <is>
-          <t>Japan NIID amoebic dysentery notifications.</t>
-        </is>
-      </c>
-      <c r="AM122" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN122" t="b">
-        <v>1</v>
+        <v>10</v>
+      </c>
+      <c r="R122" t="n">
+        <v>0.04345692446436896</v>
+      </c>
+      <c r="S122" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO122" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP122" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ122" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS122" t="inlineStr">
-        <is>
-          <t>SER_JP_AMEBIASIS_WEEKLY</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR122" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS122" t="inlineStr"/>
       <c r="AT122" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU122" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV122" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="AW122" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ122" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="BA122" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="BB122" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="BC122" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -23995,7 +23986,7 @@
       </c>
       <c r="L123" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M123" t="inlineStr">
@@ -24004,16 +23995,16 @@
         </is>
       </c>
       <c r="N123" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="O123" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="P123" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="R123" t="n">
-        <v>0.00653446726052613</v>
+        <v>0.007351275668091897</v>
       </c>
       <c r="S123" t="inlineStr">
         <is>
@@ -24157,7 +24148,7 @@
       </c>
       <c r="L124" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M124" t="inlineStr">
@@ -24166,13 +24157,13 @@
         </is>
       </c>
       <c r="N124" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="O124" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="P124" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U124" t="inlineStr">
         <is>
@@ -24394,7 +24385,7 @@
       </c>
       <c r="L125" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="M125" t="inlineStr">
@@ -24403,16 +24394,16 @@
         </is>
       </c>
       <c r="N125" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="O125" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="P125" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="R125" t="n">
-        <v>0.001633616815131532</v>
+        <v>0.00653446726052613</v>
       </c>
       <c r="S125" t="inlineStr">
         <is>
@@ -24556,7 +24547,7 @@
       </c>
       <c r="L126" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="M126" t="inlineStr">
@@ -24565,13 +24556,13 @@
         </is>
       </c>
       <c r="N126" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="O126" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="P126" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="U126" t="inlineStr">
         <is>
@@ -24793,7 +24784,7 @@
       </c>
       <c r="L127" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="M127" t="inlineStr">
@@ -24802,16 +24793,16 @@
         </is>
       </c>
       <c r="N127" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="O127" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="P127" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="R127" t="n">
-        <v>0.00898489248322343</v>
+        <v>0.001633616815131532</v>
       </c>
       <c r="S127" t="inlineStr">
         <is>
@@ -24955,7 +24946,7 @@
       </c>
       <c r="L128" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="M128" t="inlineStr">
@@ -24964,13 +24955,13 @@
         </is>
       </c>
       <c r="N128" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="O128" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="P128" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="U128" t="inlineStr">
         <is>
@@ -25192,7 +25183,7 @@
       </c>
       <c r="L129" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="M129" t="inlineStr">
@@ -25201,16 +25192,16 @@
         </is>
       </c>
       <c r="N129" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="O129" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="P129" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="R129" t="n">
-        <v>0.0008168084075657662</v>
+        <v>0.00898489248322343</v>
       </c>
       <c r="S129" t="inlineStr">
         <is>
@@ -25354,7 +25345,7 @@
       </c>
       <c r="L130" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="M130" t="inlineStr">
@@ -25363,13 +25354,13 @@
         </is>
       </c>
       <c r="N130" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="O130" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="P130" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="U130" t="inlineStr">
         <is>
@@ -25561,12 +25552,12 @@
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
@@ -25591,22 +25582,25 @@
       </c>
       <c r="L131" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="M131" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N131" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O131" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="P131" t="n">
+        <v>1</v>
       </c>
       <c r="R131" t="n">
-        <v>0</v>
+        <v>0.0008168084075657662</v>
       </c>
       <c r="S131" t="inlineStr">
         <is>
@@ -25615,12 +25609,12 @@
       </c>
       <c r="U131" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1290</t>
+          <t>SER_JP_AMEBIASIS_WEEKLY</t>
         </is>
       </c>
       <c r="AA131" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO131" t="inlineStr">
@@ -25635,12 +25629,12 @@
       </c>
       <c r="AQ131" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS131" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1290</t>
+          <t>SER_JP_AMEBIASIS_WEEKLY</t>
         </is>
       </c>
       <c r="AT131" t="n">
@@ -25648,47 +25642,47 @@
       </c>
       <c r="AU131" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV131" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW131" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX131" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY131" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ131" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA131" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB131" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC131" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -25720,12 +25714,12 @@
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
@@ -25750,38 +25744,41 @@
       </c>
       <c r="L132" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="M132" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N132" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O132" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="P132" t="n">
+        <v>1</v>
       </c>
       <c r="U132" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1290</t>
+          <t>SER_JP_AMEBIASIS_WEEKLY</t>
         </is>
       </c>
       <c r="V132" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1290</t>
+          <t>SER_JP_AMEBIASIS_WEEKLY</t>
         </is>
       </c>
       <c r="W132" t="inlineStr">
         <is>
-          <t>SRC_FI_THL_TTR</t>
+          <t>SRC_JP_NIID</t>
         </is>
       </c>
       <c r="X132" t="inlineStr">
         <is>
-          <t>Amebiasis</t>
+          <t>Amoebic dysentery</t>
         </is>
       </c>
       <c r="Y132" t="inlineStr">
@@ -25791,12 +25788,12 @@
       </c>
       <c r="Z132" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA132" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AB132" t="inlineStr">
@@ -25806,7 +25803,7 @@
       </c>
       <c r="AC132" t="inlineStr">
         <is>
-          <t>country:FI:national</t>
+          <t>country:JP:national</t>
         </is>
       </c>
       <c r="AD132" t="inlineStr">
@@ -25821,7 +25818,7 @@
       </c>
       <c r="AF132" t="inlineStr">
         <is>
-          <t>conditional</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="AG132" t="inlineStr">
@@ -25841,12 +25838,12 @@
       </c>
       <c r="AJ132" t="inlineStr">
         <is>
-          <t>FI_THL_TTR_reporting_group</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK132" t="inlineStr">
         <is>
-          <t>Finland THL national monthly notification series; THL reporting group code 1290.</t>
+          <t>Japan NIID amoebic dysentery notifications.</t>
         </is>
       </c>
       <c r="AM132" t="inlineStr">
@@ -25869,12 +25866,12 @@
       </c>
       <c r="AQ132" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS132" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1290</t>
+          <t>SER_JP_AMEBIASIS_WEEKLY</t>
         </is>
       </c>
       <c r="AT132" t="n">
@@ -25882,45 +25879,438 @@
       </c>
       <c r="AU132" t="inlineStr">
         <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV132" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW132" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX132" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY132" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ132" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA132" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB132" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC132" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>D165</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>amebiasis</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>Amebiasis</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>FI</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>D165</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>Amebiasis</t>
+        </is>
+      </c>
+      <c r="J133" t="inlineStr">
+        <is>
+          <t>阿米巴病</t>
+        </is>
+      </c>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L133" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M133" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N133" t="n">
+        <v>0</v>
+      </c>
+      <c r="O133" t="n">
+        <v>0</v>
+      </c>
+      <c r="R133" t="n">
+        <v>0</v>
+      </c>
+      <c r="S133" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U133" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1290</t>
+        </is>
+      </c>
+      <c r="AA133" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO133" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP133" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ133" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AS133" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1290</t>
+        </is>
+      </c>
+      <c r="AT133" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU133" t="inlineStr">
+        <is>
           <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
-      <c r="AV132" t="inlineStr">
+      <c r="AV133" t="inlineStr">
         <is>
           <t>thl_ttr</t>
         </is>
       </c>
-      <c r="AW132" t="inlineStr">
+      <c r="AW133" t="inlineStr">
         <is>
           <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
-      <c r="AX132" t="inlineStr">
+      <c r="AX133" t="inlineStr">
         <is>
           <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
-      <c r="AY132" t="inlineStr">
+      <c r="AY133" t="inlineStr">
         <is>
           <t>cube_csv</t>
         </is>
       </c>
-      <c r="AZ132" t="inlineStr">
+      <c r="AZ133" t="inlineStr">
         <is>
           <t>thl_ttr</t>
         </is>
       </c>
-      <c r="BA132" t="inlineStr">
+      <c r="BA133" t="inlineStr">
         <is>
           <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
-      <c r="BB132" t="inlineStr">
+      <c r="BB133" t="inlineStr">
         <is>
           <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
-      <c r="BC132" t="inlineStr">
+      <c r="BC133" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>D165</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>amebiasis</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>Amebiasis</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>FI</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>D165</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>Amebiasis</t>
+        </is>
+      </c>
+      <c r="J134" t="inlineStr">
+        <is>
+          <t>阿米巴病</t>
+        </is>
+      </c>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L134" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M134" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N134" t="n">
+        <v>0</v>
+      </c>
+      <c r="O134" t="n">
+        <v>0</v>
+      </c>
+      <c r="U134" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1290</t>
+        </is>
+      </c>
+      <c r="V134" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1290</t>
+        </is>
+      </c>
+      <c r="W134" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X134" t="inlineStr">
+        <is>
+          <t>Amebiasis</t>
+        </is>
+      </c>
+      <c r="Y134" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z134" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA134" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB134" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC134" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD134" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE134" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF134" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG134" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH134" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI134" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ134" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK134" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; THL reporting group code 1290.</t>
+        </is>
+      </c>
+      <c r="AM134" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN134" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO134" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP134" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ134" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AS134" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1290</t>
+        </is>
+      </c>
+      <c r="AT134" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU134" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
+      </c>
+      <c r="AV134" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="AW134" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="AX134" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="AY134" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+      <c r="AZ134" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="BA134" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="BB134" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="BC134" t="inlineStr">
         <is>
           <t>cube_csv</t>
         </is>
@@ -26042,7 +26432,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="10">
@@ -26052,7 +26442,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>131</v>
+        <v>133</v>
       </c>
     </row>
     <row r="11">
@@ -26072,7 +26462,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="13">
@@ -26104,7 +26494,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>514</v>
+        <v>525</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d165/2026-2029.xlsx
+++ b/diseases/d165/2026-2029.xlsx
@@ -26316,6 +26316,405 @@
         </is>
       </c>
     </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>D165</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>amebiasis</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>Amebiasis</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>D165</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>Amebiasis</t>
+        </is>
+      </c>
+      <c r="J135" t="inlineStr">
+        <is>
+          <t>阿米巴病</t>
+        </is>
+      </c>
+      <c r="K135" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L135" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="M135" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N135" t="n">
+        <v>10</v>
+      </c>
+      <c r="O135" t="n">
+        <v>10</v>
+      </c>
+      <c r="P135" t="n">
+        <v>10</v>
+      </c>
+      <c r="R135" t="n">
+        <v>0.008168084075657663</v>
+      </c>
+      <c r="S135" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U135" t="inlineStr">
+        <is>
+          <t>SER_JP_AMEBIASIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AA135" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO135" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP135" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ135" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS135" t="inlineStr">
+        <is>
+          <t>SER_JP_AMEBIASIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT135" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU135" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV135" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW135" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX135" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY135" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ135" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA135" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB135" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC135" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>D165</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>amebiasis</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>Amebiasis</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>D165</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>Amebiasis</t>
+        </is>
+      </c>
+      <c r="J136" t="inlineStr">
+        <is>
+          <t>阿米巴病</t>
+        </is>
+      </c>
+      <c r="K136" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L136" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="M136" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N136" t="n">
+        <v>10</v>
+      </c>
+      <c r="O136" t="n">
+        <v>10</v>
+      </c>
+      <c r="P136" t="n">
+        <v>10</v>
+      </c>
+      <c r="U136" t="inlineStr">
+        <is>
+          <t>SER_JP_AMEBIASIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V136" t="inlineStr">
+        <is>
+          <t>SER_JP_AMEBIASIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W136" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X136" t="inlineStr">
+        <is>
+          <t>Amoebic dysentery</t>
+        </is>
+      </c>
+      <c r="Y136" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z136" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA136" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB136" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC136" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD136" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE136" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF136" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG136" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH136" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI136" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ136" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
+        </is>
+      </c>
+      <c r="AK136" t="inlineStr">
+        <is>
+          <t>Japan NIID amoebic dysentery notifications.</t>
+        </is>
+      </c>
+      <c r="AM136" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN136" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO136" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP136" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ136" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS136" t="inlineStr">
+        <is>
+          <t>SER_JP_AMEBIASIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT136" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU136" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV136" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW136" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX136" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY136" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ136" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA136" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB136" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC136" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -26349,7 +26748,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -26432,7 +26831,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="10">
@@ -26442,7 +26841,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>133</v>
+        <v>135</v>
       </c>
     </row>
     <row r="11">
@@ -26462,7 +26861,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="13">
@@ -26494,7 +26893,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>525</v>
+        <v>535</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d165/2026-2029.xlsx
+++ b/diseases/d165/2026-2029.xlsx
@@ -2476,7 +2476,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
@@ -2878,7 +2878,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
@@ -3280,7 +3280,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -3682,7 +3682,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
@@ -5012,7 +5012,7 @@
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK24" t="inlineStr">
@@ -5955,7 +5955,7 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
@@ -6357,7 +6357,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
@@ -6759,7 +6759,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
@@ -8089,7 +8089,7 @@
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK40" t="inlineStr">
@@ -9032,7 +9032,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
@@ -9434,7 +9434,7 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK47" t="inlineStr">
@@ -9836,7 +9836,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK49" t="inlineStr">
@@ -10238,7 +10238,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
@@ -12106,7 +12106,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK61" t="inlineStr">
@@ -12508,7 +12508,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
@@ -12910,7 +12910,7 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK65" t="inlineStr">
@@ -13312,7 +13312,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
@@ -15180,7 +15180,7 @@
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK77" t="inlineStr">
@@ -15582,7 +15582,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK79" t="inlineStr">
@@ -15984,7 +15984,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK81" t="inlineStr">
@@ -16386,7 +16386,7 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK83" t="inlineStr">
@@ -16788,7 +16788,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK85" t="inlineStr">
@@ -18653,7 +18653,7 @@
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK95" t="inlineStr">
@@ -19052,7 +19052,7 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK97" t="inlineStr">
@@ -19451,7 +19451,7 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK99" t="inlineStr">
@@ -19850,7 +19850,7 @@
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK101" t="inlineStr">
@@ -21715,7 +21715,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK111" t="inlineStr">
@@ -22114,7 +22114,7 @@
       </c>
       <c r="AJ113" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK113" t="inlineStr">
@@ -22513,7 +22513,7 @@
       </c>
       <c r="AJ115" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK115" t="inlineStr">
@@ -22912,7 +22912,7 @@
       </c>
       <c r="AJ117" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK117" t="inlineStr">
@@ -23418,12 +23418,12 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -23463,89 +23463,75 @@
         <v>1</v>
       </c>
       <c r="R120" t="n">
-        <v>0.009344880428283346</v>
+        <v>0.01355270280196709</v>
       </c>
       <c r="S120" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U120" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_ENTAMOEBA</t>
-        </is>
-      </c>
-      <c r="AA120" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO120" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP120" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ120" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS120" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_ENTAMOEBA</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR120" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS120" t="inlineStr"/>
       <c r="AT120" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU120" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV120" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW120" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY120" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ120" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA120" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB120" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC120" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -23572,7 +23558,7 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -23621,98 +23607,23 @@
       <c r="O121" t="n">
         <v>1</v>
       </c>
+      <c r="R121" t="n">
+        <v>0.009344880428283346</v>
+      </c>
+      <c r="S121" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U121" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_ENTAMOEBA</t>
         </is>
       </c>
-      <c r="V121" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_ENTAMOEBA</t>
-        </is>
-      </c>
-      <c r="W121" t="inlineStr">
-        <is>
-          <t>SRC_SE_FOHM_SMINET</t>
-        </is>
-      </c>
-      <c r="X121" t="inlineStr">
-        <is>
-          <t>Entamoeba histolytica</t>
-        </is>
-      </c>
-      <c r="Y121" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z121" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA121" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB121" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC121" t="inlineStr">
-        <is>
-          <t>country:SE:national</t>
-        </is>
-      </c>
-      <c r="AD121" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE121" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF121" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG121" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH121" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI121" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ121" t="inlineStr">
-        <is>
-          <t>SE_FOHM_SMINET_current</t>
-        </is>
-      </c>
-      <c r="AK121" t="inlineStr">
-        <is>
-          <t>Sweden FHM SmiNet national monthly notification series; FHM Entamoeba histolytica source category.</t>
-        </is>
-      </c>
-      <c r="AM121" t="inlineStr">
-        <is>
-          <t>revised</t>
-        </is>
-      </c>
-      <c r="AN121" t="b">
-        <v>1</v>
       </c>
       <c r="AO121" t="inlineStr">
         <is>
@@ -23806,17 +23717,17 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Taiwan, China</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
@@ -23850,81 +23761,170 @@
         </is>
       </c>
       <c r="N122" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="O122" t="n">
-        <v>10</v>
-      </c>
-      <c r="R122" t="n">
-        <v>0.04345692446436896</v>
-      </c>
-      <c r="S122" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="U122" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_ENTAMOEBA</t>
+        </is>
+      </c>
+      <c r="V122" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_ENTAMOEBA</t>
+        </is>
+      </c>
+      <c r="W122" t="inlineStr">
+        <is>
+          <t>SRC_SE_FOHM_SMINET</t>
+        </is>
+      </c>
+      <c r="X122" t="inlineStr">
+        <is>
+          <t>Entamoeba histolytica</t>
+        </is>
+      </c>
+      <c r="Y122" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z122" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA122" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB122" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC122" t="inlineStr">
+        <is>
+          <t>country:SE:national</t>
+        </is>
+      </c>
+      <c r="AD122" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE122" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF122" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG122" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH122" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI122" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ122" t="inlineStr">
+        <is>
+          <t>SE_FOHM_SMINET_current</t>
+        </is>
+      </c>
+      <c r="AK122" t="inlineStr">
+        <is>
+          <t>Sweden FHM SmiNet national monthly notification series; FHM Entamoeba histolytica source category.</t>
+        </is>
+      </c>
+      <c r="AM122" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN122" t="b">
+        <v>1</v>
       </c>
       <c r="AO122" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP122" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR122" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS122" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ122" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS122" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_ENTAMOEBA</t>
+        </is>
+      </c>
       <c r="AT122" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU122" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV122" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW122" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ122" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA122" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB122" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC122" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -23956,12 +23956,12 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>TW</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Taiwan, China</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
@@ -23986,7 +23986,7 @@
       </c>
       <c r="L123" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M123" t="inlineStr">
@@ -23995,98 +23995,81 @@
         </is>
       </c>
       <c r="N123" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O123" t="n">
-        <v>9</v>
-      </c>
-      <c r="P123" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="R123" t="n">
-        <v>0.007351275668091897</v>
+        <v>0.04345692446436896</v>
       </c>
       <c r="S123" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U123" t="inlineStr">
-        <is>
-          <t>SER_JP_AMEBIASIS_WEEKLY</t>
-        </is>
-      </c>
-      <c r="AA123" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO123" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP123" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ123" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS123" t="inlineStr">
-        <is>
-          <t>SER_JP_AMEBIASIS_WEEKLY</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR123" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS123" t="inlineStr"/>
       <c r="AT123" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU123" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV123" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="AW123" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="AY123" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ123" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="BA123" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="BB123" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="BC123" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -24113,7 +24096,7 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -24165,98 +24148,23 @@
       <c r="P124" t="n">
         <v>9</v>
       </c>
+      <c r="R124" t="n">
+        <v>0.007351275668091897</v>
+      </c>
+      <c r="S124" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U124" t="inlineStr">
         <is>
           <t>SER_JP_AMEBIASIS_WEEKLY</t>
         </is>
       </c>
-      <c r="V124" t="inlineStr">
-        <is>
-          <t>SER_JP_AMEBIASIS_WEEKLY</t>
-        </is>
-      </c>
-      <c r="W124" t="inlineStr">
-        <is>
-          <t>SRC_JP_NIID</t>
-        </is>
-      </c>
-      <c r="X124" t="inlineStr">
-        <is>
-          <t>Amoebic dysentery</t>
-        </is>
-      </c>
-      <c r="Y124" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z124" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
       <c r="AA124" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB124" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC124" t="inlineStr">
-        <is>
-          <t>country:JP:national</t>
-        </is>
-      </c>
-      <c r="AD124" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE124" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF124" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG124" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH124" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI124" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ124" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
-        </is>
-      </c>
-      <c r="AK124" t="inlineStr">
-        <is>
-          <t>Japan NIID amoebic dysentery notifications.</t>
-        </is>
-      </c>
-      <c r="AM124" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN124" t="b">
-        <v>1</v>
       </c>
       <c r="AO124" t="inlineStr">
         <is>
@@ -24350,7 +24258,7 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -24385,7 +24293,7 @@
       </c>
       <c r="L125" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M125" t="inlineStr">
@@ -24394,31 +24302,106 @@
         </is>
       </c>
       <c r="N125" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="O125" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="P125" t="n">
-        <v>8</v>
-      </c>
-      <c r="R125" t="n">
-        <v>0.00653446726052613</v>
-      </c>
-      <c r="S125" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>9</v>
       </c>
       <c r="U125" t="inlineStr">
         <is>
           <t>SER_JP_AMEBIASIS_WEEKLY</t>
         </is>
       </c>
+      <c r="V125" t="inlineStr">
+        <is>
+          <t>SER_JP_AMEBIASIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W125" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X125" t="inlineStr">
+        <is>
+          <t>Amoebic dysentery</t>
+        </is>
+      </c>
+      <c r="Y125" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z125" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
       <c r="AA125" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
+      </c>
+      <c r="AB125" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC125" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD125" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE125" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF125" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG125" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH125" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI125" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ125" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
+        </is>
+      </c>
+      <c r="AK125" t="inlineStr">
+        <is>
+          <t>Japan NIID amoebic dysentery notifications.</t>
+        </is>
+      </c>
+      <c r="AM125" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN125" t="b">
+        <v>1</v>
       </c>
       <c r="AO125" t="inlineStr">
         <is>
@@ -24512,7 +24495,7 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -24564,98 +24547,23 @@
       <c r="P126" t="n">
         <v>8</v>
       </c>
+      <c r="R126" t="n">
+        <v>0.00653446726052613</v>
+      </c>
+      <c r="S126" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U126" t="inlineStr">
         <is>
           <t>SER_JP_AMEBIASIS_WEEKLY</t>
         </is>
       </c>
-      <c r="V126" t="inlineStr">
-        <is>
-          <t>SER_JP_AMEBIASIS_WEEKLY</t>
-        </is>
-      </c>
-      <c r="W126" t="inlineStr">
-        <is>
-          <t>SRC_JP_NIID</t>
-        </is>
-      </c>
-      <c r="X126" t="inlineStr">
-        <is>
-          <t>Amoebic dysentery</t>
-        </is>
-      </c>
-      <c r="Y126" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z126" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
       <c r="AA126" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB126" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC126" t="inlineStr">
-        <is>
-          <t>country:JP:national</t>
-        </is>
-      </c>
-      <c r="AD126" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE126" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF126" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG126" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH126" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI126" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ126" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
-        </is>
-      </c>
-      <c r="AK126" t="inlineStr">
-        <is>
-          <t>Japan NIID amoebic dysentery notifications.</t>
-        </is>
-      </c>
-      <c r="AM126" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN126" t="b">
-        <v>1</v>
       </c>
       <c r="AO126" t="inlineStr">
         <is>
@@ -24749,7 +24657,7 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -24784,7 +24692,7 @@
       </c>
       <c r="L127" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="M127" t="inlineStr">
@@ -24793,31 +24701,106 @@
         </is>
       </c>
       <c r="N127" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="O127" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="P127" t="n">
-        <v>2</v>
-      </c>
-      <c r="R127" t="n">
-        <v>0.001633616815131532</v>
-      </c>
-      <c r="S127" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>8</v>
       </c>
       <c r="U127" t="inlineStr">
         <is>
           <t>SER_JP_AMEBIASIS_WEEKLY</t>
         </is>
       </c>
+      <c r="V127" t="inlineStr">
+        <is>
+          <t>SER_JP_AMEBIASIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W127" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X127" t="inlineStr">
+        <is>
+          <t>Amoebic dysentery</t>
+        </is>
+      </c>
+      <c r="Y127" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z127" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
       <c r="AA127" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
+      </c>
+      <c r="AB127" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC127" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD127" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE127" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF127" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG127" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH127" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI127" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ127" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
+        </is>
+      </c>
+      <c r="AK127" t="inlineStr">
+        <is>
+          <t>Japan NIID amoebic dysentery notifications.</t>
+        </is>
+      </c>
+      <c r="AM127" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN127" t="b">
+        <v>1</v>
       </c>
       <c r="AO127" t="inlineStr">
         <is>
@@ -24911,7 +24894,7 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -24963,98 +24946,23 @@
       <c r="P128" t="n">
         <v>2</v>
       </c>
+      <c r="R128" t="n">
+        <v>0.001633616815131532</v>
+      </c>
+      <c r="S128" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U128" t="inlineStr">
         <is>
           <t>SER_JP_AMEBIASIS_WEEKLY</t>
         </is>
       </c>
-      <c r="V128" t="inlineStr">
-        <is>
-          <t>SER_JP_AMEBIASIS_WEEKLY</t>
-        </is>
-      </c>
-      <c r="W128" t="inlineStr">
-        <is>
-          <t>SRC_JP_NIID</t>
-        </is>
-      </c>
-      <c r="X128" t="inlineStr">
-        <is>
-          <t>Amoebic dysentery</t>
-        </is>
-      </c>
-      <c r="Y128" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z128" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
       <c r="AA128" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB128" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC128" t="inlineStr">
-        <is>
-          <t>country:JP:national</t>
-        </is>
-      </c>
-      <c r="AD128" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE128" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF128" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG128" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH128" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI128" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ128" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
-        </is>
-      </c>
-      <c r="AK128" t="inlineStr">
-        <is>
-          <t>Japan NIID amoebic dysentery notifications.</t>
-        </is>
-      </c>
-      <c r="AM128" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN128" t="b">
-        <v>1</v>
       </c>
       <c r="AO128" t="inlineStr">
         <is>
@@ -25148,7 +25056,7 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -25183,7 +25091,7 @@
       </c>
       <c r="L129" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="M129" t="inlineStr">
@@ -25192,31 +25100,106 @@
         </is>
       </c>
       <c r="N129" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="O129" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="P129" t="n">
-        <v>11</v>
-      </c>
-      <c r="R129" t="n">
-        <v>0.00898489248322343</v>
-      </c>
-      <c r="S129" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>2</v>
       </c>
       <c r="U129" t="inlineStr">
         <is>
           <t>SER_JP_AMEBIASIS_WEEKLY</t>
         </is>
       </c>
+      <c r="V129" t="inlineStr">
+        <is>
+          <t>SER_JP_AMEBIASIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W129" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X129" t="inlineStr">
+        <is>
+          <t>Amoebic dysentery</t>
+        </is>
+      </c>
+      <c r="Y129" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z129" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
       <c r="AA129" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
+      </c>
+      <c r="AB129" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC129" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD129" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE129" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF129" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG129" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH129" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI129" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ129" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
+        </is>
+      </c>
+      <c r="AK129" t="inlineStr">
+        <is>
+          <t>Japan NIID amoebic dysentery notifications.</t>
+        </is>
+      </c>
+      <c r="AM129" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN129" t="b">
+        <v>1</v>
       </c>
       <c r="AO129" t="inlineStr">
         <is>
@@ -25310,7 +25293,7 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
@@ -25362,98 +25345,23 @@
       <c r="P130" t="n">
         <v>11</v>
       </c>
+      <c r="R130" t="n">
+        <v>0.00898489248322343</v>
+      </c>
+      <c r="S130" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U130" t="inlineStr">
         <is>
           <t>SER_JP_AMEBIASIS_WEEKLY</t>
         </is>
       </c>
-      <c r="V130" t="inlineStr">
-        <is>
-          <t>SER_JP_AMEBIASIS_WEEKLY</t>
-        </is>
-      </c>
-      <c r="W130" t="inlineStr">
-        <is>
-          <t>SRC_JP_NIID</t>
-        </is>
-      </c>
-      <c r="X130" t="inlineStr">
-        <is>
-          <t>Amoebic dysentery</t>
-        </is>
-      </c>
-      <c r="Y130" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z130" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
       <c r="AA130" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB130" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC130" t="inlineStr">
-        <is>
-          <t>country:JP:national</t>
-        </is>
-      </c>
-      <c r="AD130" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE130" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF130" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG130" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH130" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI130" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ130" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
-        </is>
-      </c>
-      <c r="AK130" t="inlineStr">
-        <is>
-          <t>Japan NIID amoebic dysentery notifications.</t>
-        </is>
-      </c>
-      <c r="AM130" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN130" t="b">
-        <v>1</v>
       </c>
       <c r="AO130" t="inlineStr">
         <is>
@@ -25547,7 +25455,7 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
@@ -25582,7 +25490,7 @@
       </c>
       <c r="L131" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="M131" t="inlineStr">
@@ -25591,31 +25499,106 @@
         </is>
       </c>
       <c r="N131" t="n">
+        <v>11</v>
+      </c>
+      <c r="O131" t="n">
+        <v>11</v>
+      </c>
+      <c r="P131" t="n">
+        <v>11</v>
+      </c>
+      <c r="U131" t="inlineStr">
+        <is>
+          <t>SER_JP_AMEBIASIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V131" t="inlineStr">
+        <is>
+          <t>SER_JP_AMEBIASIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W131" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X131" t="inlineStr">
+        <is>
+          <t>Amoebic dysentery</t>
+        </is>
+      </c>
+      <c r="Y131" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z131" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA131" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB131" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC131" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD131" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE131" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF131" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG131" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH131" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI131" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ131" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
+        </is>
+      </c>
+      <c r="AK131" t="inlineStr">
+        <is>
+          <t>Japan NIID amoebic dysentery notifications.</t>
+        </is>
+      </c>
+      <c r="AM131" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN131" t="b">
         <v>1</v>
-      </c>
-      <c r="O131" t="n">
-        <v>1</v>
-      </c>
-      <c r="P131" t="n">
-        <v>1</v>
-      </c>
-      <c r="R131" t="n">
-        <v>0.0008168084075657662</v>
-      </c>
-      <c r="S131" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="U131" t="inlineStr">
-        <is>
-          <t>SER_JP_AMEBIASIS_WEEKLY</t>
-        </is>
-      </c>
-      <c r="AA131" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
       </c>
       <c r="AO131" t="inlineStr">
         <is>
@@ -25709,7 +25692,7 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
@@ -25761,98 +25744,23 @@
       <c r="P132" t="n">
         <v>1</v>
       </c>
+      <c r="R132" t="n">
+        <v>0.0008168084075657662</v>
+      </c>
+      <c r="S132" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U132" t="inlineStr">
         <is>
           <t>SER_JP_AMEBIASIS_WEEKLY</t>
         </is>
       </c>
-      <c r="V132" t="inlineStr">
-        <is>
-          <t>SER_JP_AMEBIASIS_WEEKLY</t>
-        </is>
-      </c>
-      <c r="W132" t="inlineStr">
-        <is>
-          <t>SRC_JP_NIID</t>
-        </is>
-      </c>
-      <c r="X132" t="inlineStr">
-        <is>
-          <t>Amoebic dysentery</t>
-        </is>
-      </c>
-      <c r="Y132" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z132" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
       <c r="AA132" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB132" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC132" t="inlineStr">
-        <is>
-          <t>country:JP:national</t>
-        </is>
-      </c>
-      <c r="AD132" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE132" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF132" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG132" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH132" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI132" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ132" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
-        </is>
-      </c>
-      <c r="AK132" t="inlineStr">
-        <is>
-          <t>Japan NIID amoebic dysentery notifications.</t>
-        </is>
-      </c>
-      <c r="AM132" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN132" t="b">
-        <v>1</v>
       </c>
       <c r="AO132" t="inlineStr">
         <is>
@@ -25946,17 +25854,17 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
@@ -25981,37 +25889,115 @@
       </c>
       <c r="L133" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="M133" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N133" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O133" t="n">
-        <v>0</v>
-      </c>
-      <c r="R133" t="n">
-        <v>0</v>
-      </c>
-      <c r="S133" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="P133" t="n">
+        <v>1</v>
       </c>
       <c r="U133" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1290</t>
+          <t>SER_JP_AMEBIASIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V133" t="inlineStr">
+        <is>
+          <t>SER_JP_AMEBIASIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W133" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X133" t="inlineStr">
+        <is>
+          <t>Amoebic dysentery</t>
+        </is>
+      </c>
+      <c r="Y133" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z133" t="inlineStr">
+        <is>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA133" t="inlineStr">
         <is>
-          <t>monthly</t>
-        </is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB133" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC133" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD133" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE133" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF133" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG133" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH133" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI133" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ133" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
+        </is>
+      </c>
+      <c r="AK133" t="inlineStr">
+        <is>
+          <t>Japan NIID amoebic dysentery notifications.</t>
+        </is>
+      </c>
+      <c r="AM133" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN133" t="b">
+        <v>1</v>
       </c>
       <c r="AO133" t="inlineStr">
         <is>
@@ -26025,12 +26011,12 @@
       </c>
       <c r="AQ133" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS133" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1290</t>
+          <t>SER_JP_AMEBIASIS_WEEKLY</t>
         </is>
       </c>
       <c r="AT133" t="n">
@@ -26038,47 +26024,47 @@
       </c>
       <c r="AU133" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV133" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW133" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX133" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY133" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ133" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA133" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB133" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC133" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -26105,7 +26091,7 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
@@ -26154,98 +26140,23 @@
       <c r="O134" t="n">
         <v>0</v>
       </c>
+      <c r="R134" t="n">
+        <v>0</v>
+      </c>
+      <c r="S134" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U134" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1290</t>
         </is>
       </c>
-      <c r="V134" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1290</t>
-        </is>
-      </c>
-      <c r="W134" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X134" t="inlineStr">
-        <is>
-          <t>Amebiasis</t>
-        </is>
-      </c>
-      <c r="Y134" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z134" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA134" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB134" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC134" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD134" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE134" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF134" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG134" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH134" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI134" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ134" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK134" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; THL reporting group code 1290.</t>
-        </is>
-      </c>
-      <c r="AM134" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN134" t="b">
-        <v>1</v>
       </c>
       <c r="AO134" t="inlineStr">
         <is>
@@ -26339,17 +26250,17 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
@@ -26374,7 +26285,7 @@
       </c>
       <c r="L135" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="M135" t="inlineStr">
@@ -26383,31 +26294,103 @@
         </is>
       </c>
       <c r="N135" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="O135" t="n">
-        <v>10</v>
-      </c>
-      <c r="P135" t="n">
-        <v>10</v>
-      </c>
-      <c r="R135" t="n">
-        <v>0.008168084075657663</v>
-      </c>
-      <c r="S135" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>0</v>
       </c>
       <c r="U135" t="inlineStr">
         <is>
-          <t>SER_JP_AMEBIASIS_WEEKLY</t>
+          <t>SER_FI_THL_TTR_1290</t>
+        </is>
+      </c>
+      <c r="V135" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1290</t>
+        </is>
+      </c>
+      <c r="W135" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X135" t="inlineStr">
+        <is>
+          <t>Amebiasis</t>
+        </is>
+      </c>
+      <c r="Y135" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z135" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA135" t="inlineStr">
         <is>
-          <t>weekly</t>
-        </is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB135" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC135" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD135" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE135" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF135" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG135" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH135" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI135" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ135" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK135" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; THL reporting group code 1290.</t>
+        </is>
+      </c>
+      <c r="AM135" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN135" t="b">
+        <v>1</v>
       </c>
       <c r="AO135" t="inlineStr">
         <is>
@@ -26421,12 +26404,12 @@
       </c>
       <c r="AQ135" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AS135" t="inlineStr">
         <is>
-          <t>SER_JP_AMEBIASIS_WEEKLY</t>
+          <t>SER_FI_THL_TTR_1290</t>
         </is>
       </c>
       <c r="AT135" t="n">
@@ -26434,47 +26417,47 @@
       </c>
       <c r="AU135" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV135" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW135" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX135" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY135" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ135" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA135" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB135" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC135" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -26501,7 +26484,7 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
@@ -26553,98 +26536,23 @@
       <c r="P136" t="n">
         <v>10</v>
       </c>
+      <c r="R136" t="n">
+        <v>0.008168084075657663</v>
+      </c>
+      <c r="S136" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U136" t="inlineStr">
         <is>
           <t>SER_JP_AMEBIASIS_WEEKLY</t>
         </is>
       </c>
-      <c r="V136" t="inlineStr">
-        <is>
-          <t>SER_JP_AMEBIASIS_WEEKLY</t>
-        </is>
-      </c>
-      <c r="W136" t="inlineStr">
-        <is>
-          <t>SRC_JP_NIID</t>
-        </is>
-      </c>
-      <c r="X136" t="inlineStr">
-        <is>
-          <t>Amoebic dysentery</t>
-        </is>
-      </c>
-      <c r="Y136" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z136" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
       <c r="AA136" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB136" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC136" t="inlineStr">
-        <is>
-          <t>country:JP:national</t>
-        </is>
-      </c>
-      <c r="AD136" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE136" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF136" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG136" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH136" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI136" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ136" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
-        </is>
-      </c>
-      <c r="AK136" t="inlineStr">
-        <is>
-          <t>Japan NIID amoebic dysentery notifications.</t>
-        </is>
-      </c>
-      <c r="AM136" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN136" t="b">
-        <v>1</v>
       </c>
       <c r="AO136" t="inlineStr">
         <is>
@@ -26710,6 +26618,642 @@
         </is>
       </c>
       <c r="BC136" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>D165</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>amebiasis</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>Amebiasis</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>D165</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>Amebiasis</t>
+        </is>
+      </c>
+      <c r="J137" t="inlineStr">
+        <is>
+          <t>阿米巴病</t>
+        </is>
+      </c>
+      <c r="K137" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L137" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="M137" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N137" t="n">
+        <v>10</v>
+      </c>
+      <c r="O137" t="n">
+        <v>10</v>
+      </c>
+      <c r="P137" t="n">
+        <v>10</v>
+      </c>
+      <c r="U137" t="inlineStr">
+        <is>
+          <t>SER_JP_AMEBIASIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V137" t="inlineStr">
+        <is>
+          <t>SER_JP_AMEBIASIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W137" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X137" t="inlineStr">
+        <is>
+          <t>Amoebic dysentery</t>
+        </is>
+      </c>
+      <c r="Y137" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z137" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA137" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB137" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC137" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD137" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE137" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF137" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG137" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH137" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI137" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ137" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
+        </is>
+      </c>
+      <c r="AK137" t="inlineStr">
+        <is>
+          <t>Japan NIID amoebic dysentery notifications.</t>
+        </is>
+      </c>
+      <c r="AM137" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN137" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO137" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP137" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ137" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS137" t="inlineStr">
+        <is>
+          <t>SER_JP_AMEBIASIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT137" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU137" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV137" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW137" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX137" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY137" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ137" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA137" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB137" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC137" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>D165</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>amebiasis</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>Amebiasis</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>D165</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>Amebiasis</t>
+        </is>
+      </c>
+      <c r="J138" t="inlineStr">
+        <is>
+          <t>阿米巴病</t>
+        </is>
+      </c>
+      <c r="K138" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L138" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="M138" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N138" t="n">
+        <v>10</v>
+      </c>
+      <c r="O138" t="n">
+        <v>10</v>
+      </c>
+      <c r="P138" t="n">
+        <v>10</v>
+      </c>
+      <c r="R138" t="n">
+        <v>0.008168084075657663</v>
+      </c>
+      <c r="S138" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U138" t="inlineStr">
+        <is>
+          <t>SER_JP_AMEBIASIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AA138" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO138" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP138" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ138" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS138" t="inlineStr">
+        <is>
+          <t>SER_JP_AMEBIASIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT138" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU138" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV138" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW138" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX138" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY138" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ138" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA138" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB138" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC138" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>D165</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>amebiasis</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>Amebiasis</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>D165</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>Amebiasis</t>
+        </is>
+      </c>
+      <c r="J139" t="inlineStr">
+        <is>
+          <t>阿米巴病</t>
+        </is>
+      </c>
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L139" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="M139" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N139" t="n">
+        <v>10</v>
+      </c>
+      <c r="O139" t="n">
+        <v>10</v>
+      </c>
+      <c r="P139" t="n">
+        <v>10</v>
+      </c>
+      <c r="U139" t="inlineStr">
+        <is>
+          <t>SER_JP_AMEBIASIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V139" t="inlineStr">
+        <is>
+          <t>SER_JP_AMEBIASIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W139" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X139" t="inlineStr">
+        <is>
+          <t>Amoebic dysentery</t>
+        </is>
+      </c>
+      <c r="Y139" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z139" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA139" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB139" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC139" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD139" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE139" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF139" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG139" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH139" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI139" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ139" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
+        </is>
+      </c>
+      <c r="AK139" t="inlineStr">
+        <is>
+          <t>Japan NIID amoebic dysentery notifications.</t>
+        </is>
+      </c>
+      <c r="AM139" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN139" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO139" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP139" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ139" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS139" t="inlineStr">
+        <is>
+          <t>SER_JP_AMEBIASIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT139" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU139" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV139" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW139" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX139" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY139" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ139" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA139" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB139" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC139" t="inlineStr">
         <is>
           <t>web</t>
         </is>
@@ -26748,7 +27292,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -26831,7 +27375,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>75</v>
+        <v>77</v>
       </c>
     </row>
     <row r="10">
@@ -26841,7 +27385,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>135</v>
+        <v>138</v>
       </c>
     </row>
     <row r="11">
@@ -26861,7 +27405,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="13">
@@ -26893,7 +27437,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>535</v>
+        <v>546</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d165/2026-2029.xlsx
+++ b/diseases/d165/2026-2029.xlsx
@@ -27259,6 +27259,798 @@
         </is>
       </c>
     </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>D165</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>amebiasis</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>Amebiasis</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>D165</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>Amebiasis</t>
+        </is>
+      </c>
+      <c r="J140" t="inlineStr">
+        <is>
+          <t>阿米巴病</t>
+        </is>
+      </c>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L140" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="M140" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N140" t="n">
+        <v>9</v>
+      </c>
+      <c r="O140" t="n">
+        <v>9</v>
+      </c>
+      <c r="P140" t="n">
+        <v>9</v>
+      </c>
+      <c r="R140" t="n">
+        <v>0.007351275668091897</v>
+      </c>
+      <c r="S140" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U140" t="inlineStr">
+        <is>
+          <t>SER_JP_AMEBIASIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AA140" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO140" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP140" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ140" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS140" t="inlineStr">
+        <is>
+          <t>SER_JP_AMEBIASIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT140" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU140" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV140" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW140" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX140" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY140" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ140" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA140" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB140" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC140" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>D165</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>amebiasis</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>Amebiasis</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>D165</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>Amebiasis</t>
+        </is>
+      </c>
+      <c r="J141" t="inlineStr">
+        <is>
+          <t>阿米巴病</t>
+        </is>
+      </c>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L141" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="M141" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N141" t="n">
+        <v>9</v>
+      </c>
+      <c r="O141" t="n">
+        <v>9</v>
+      </c>
+      <c r="P141" t="n">
+        <v>9</v>
+      </c>
+      <c r="U141" t="inlineStr">
+        <is>
+          <t>SER_JP_AMEBIASIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V141" t="inlineStr">
+        <is>
+          <t>SER_JP_AMEBIASIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W141" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X141" t="inlineStr">
+        <is>
+          <t>Amoebic dysentery</t>
+        </is>
+      </c>
+      <c r="Y141" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z141" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA141" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB141" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC141" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD141" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE141" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF141" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG141" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH141" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI141" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ141" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
+        </is>
+      </c>
+      <c r="AK141" t="inlineStr">
+        <is>
+          <t>Japan NIID amoebic dysentery notifications.</t>
+        </is>
+      </c>
+      <c r="AM141" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN141" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO141" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP141" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ141" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS141" t="inlineStr">
+        <is>
+          <t>SER_JP_AMEBIASIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT141" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU141" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV141" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW141" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX141" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY141" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ141" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA141" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB141" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC141" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>D165</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>amebiasis</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>Amebiasis</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>FI</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>D165</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>Amebiasis</t>
+        </is>
+      </c>
+      <c r="J142" t="inlineStr">
+        <is>
+          <t>阿米巴病</t>
+        </is>
+      </c>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L142" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="M142" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N142" t="n">
+        <v>0</v>
+      </c>
+      <c r="O142" t="n">
+        <v>0</v>
+      </c>
+      <c r="R142" t="n">
+        <v>0</v>
+      </c>
+      <c r="S142" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U142" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1290</t>
+        </is>
+      </c>
+      <c r="AA142" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO142" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP142" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ142" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AS142" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1290</t>
+        </is>
+      </c>
+      <c r="AT142" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU142" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
+      </c>
+      <c r="AV142" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="AW142" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="AX142" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="AY142" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+      <c r="AZ142" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="BA142" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="BB142" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="BC142" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>D165</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>amebiasis</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>Amebiasis</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>FI</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>D165</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>Amebiasis</t>
+        </is>
+      </c>
+      <c r="J143" t="inlineStr">
+        <is>
+          <t>阿米巴病</t>
+        </is>
+      </c>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L143" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="M143" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N143" t="n">
+        <v>0</v>
+      </c>
+      <c r="O143" t="n">
+        <v>0</v>
+      </c>
+      <c r="U143" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1290</t>
+        </is>
+      </c>
+      <c r="V143" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1290</t>
+        </is>
+      </c>
+      <c r="W143" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X143" t="inlineStr">
+        <is>
+          <t>Amebiasis</t>
+        </is>
+      </c>
+      <c r="Y143" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z143" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA143" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB143" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC143" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD143" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE143" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF143" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG143" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH143" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI143" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ143" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK143" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; THL reporting group code 1290.</t>
+        </is>
+      </c>
+      <c r="AM143" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN143" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO143" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP143" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ143" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AS143" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1290</t>
+        </is>
+      </c>
+      <c r="AT143" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU143" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
+      </c>
+      <c r="AV143" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="AW143" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="AX143" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="AY143" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+      <c r="AZ143" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="BA143" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="BB143" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="BC143" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -27292,7 +28084,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-10-01</t>
         </is>
       </c>
     </row>
@@ -27375,7 +28167,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>77</v>
+        <v>79</v>
       </c>
     </row>
     <row r="10">
@@ -27385,7 +28177,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>138</v>
+        <v>142</v>
       </c>
     </row>
     <row r="11">
@@ -27405,7 +28197,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="13">
@@ -27437,7 +28229,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>546</v>
+        <v>555</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d165/2026-2029.xlsx
+++ b/diseases/d165/2026-2029.xlsx
@@ -27686,12 +27686,12 @@
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
@@ -27716,22 +27716,25 @@
       </c>
       <c r="L142" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="M142" t="inlineStr">
         <is>
-          <t>2026-10</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="N142" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O142" t="n">
-        <v>0</v>
+        <v>4</v>
+      </c>
+      <c r="P142" t="n">
+        <v>4</v>
       </c>
       <c r="R142" t="n">
-        <v>0</v>
+        <v>0.003267233630263065</v>
       </c>
       <c r="S142" t="inlineStr">
         <is>
@@ -27740,12 +27743,12 @@
       </c>
       <c r="U142" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1290</t>
+          <t>SER_JP_AMEBIASIS_WEEKLY</t>
         </is>
       </c>
       <c r="AA142" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO142" t="inlineStr">
@@ -27760,12 +27763,12 @@
       </c>
       <c r="AQ142" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS142" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1290</t>
+          <t>SER_JP_AMEBIASIS_WEEKLY</t>
         </is>
       </c>
       <c r="AT142" t="n">
@@ -27773,47 +27776,47 @@
       </c>
       <c r="AU142" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV142" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW142" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX142" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY142" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ142" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA142" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB142" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC142" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -27845,12 +27848,12 @@
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
@@ -27875,38 +27878,41 @@
       </c>
       <c r="L143" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="M143" t="inlineStr">
         <is>
-          <t>2026-10</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="N143" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O143" t="n">
-        <v>0</v>
+        <v>4</v>
+      </c>
+      <c r="P143" t="n">
+        <v>4</v>
       </c>
       <c r="U143" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1290</t>
+          <t>SER_JP_AMEBIASIS_WEEKLY</t>
         </is>
       </c>
       <c r="V143" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1290</t>
+          <t>SER_JP_AMEBIASIS_WEEKLY</t>
         </is>
       </c>
       <c r="W143" t="inlineStr">
         <is>
-          <t>SRC_FI_THL_TTR</t>
+          <t>SRC_JP_NIID</t>
         </is>
       </c>
       <c r="X143" t="inlineStr">
         <is>
-          <t>Amebiasis</t>
+          <t>Amoebic dysentery</t>
         </is>
       </c>
       <c r="Y143" t="inlineStr">
@@ -27916,12 +27922,12 @@
       </c>
       <c r="Z143" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA143" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AB143" t="inlineStr">
@@ -27931,7 +27937,7 @@
       </c>
       <c r="AC143" t="inlineStr">
         <is>
-          <t>country:FI:national</t>
+          <t>country:JP:national</t>
         </is>
       </c>
       <c r="AD143" t="inlineStr">
@@ -27946,7 +27952,7 @@
       </c>
       <c r="AF143" t="inlineStr">
         <is>
-          <t>conditional</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="AG143" t="inlineStr">
@@ -27966,12 +27972,12 @@
       </c>
       <c r="AJ143" t="inlineStr">
         <is>
-          <t>FI_THL_TTR_reporting_group</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK143" t="inlineStr">
         <is>
-          <t>Finland THL national monthly notification series; THL reporting group code 1290.</t>
+          <t>Japan NIID amoebic dysentery notifications.</t>
         </is>
       </c>
       <c r="AM143" t="inlineStr">
@@ -27994,12 +28000,12 @@
       </c>
       <c r="AQ143" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS143" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1290</t>
+          <t>SER_JP_AMEBIASIS_WEEKLY</t>
         </is>
       </c>
       <c r="AT143" t="n">
@@ -28007,45 +28013,438 @@
       </c>
       <c r="AU143" t="inlineStr">
         <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV143" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW143" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX143" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY143" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ143" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA143" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB143" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC143" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>D165</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>amebiasis</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>Amebiasis</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>FI</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>D165</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>Amebiasis</t>
+        </is>
+      </c>
+      <c r="J144" t="inlineStr">
+        <is>
+          <t>阿米巴病</t>
+        </is>
+      </c>
+      <c r="K144" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L144" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="M144" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N144" t="n">
+        <v>0</v>
+      </c>
+      <c r="O144" t="n">
+        <v>0</v>
+      </c>
+      <c r="R144" t="n">
+        <v>0</v>
+      </c>
+      <c r="S144" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U144" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1290</t>
+        </is>
+      </c>
+      <c r="AA144" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO144" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP144" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ144" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AS144" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1290</t>
+        </is>
+      </c>
+      <c r="AT144" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU144" t="inlineStr">
+        <is>
           <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
-      <c r="AV143" t="inlineStr">
+      <c r="AV144" t="inlineStr">
         <is>
           <t>thl_ttr</t>
         </is>
       </c>
-      <c r="AW143" t="inlineStr">
+      <c r="AW144" t="inlineStr">
         <is>
           <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
-      <c r="AX143" t="inlineStr">
+      <c r="AX144" t="inlineStr">
         <is>
           <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
-      <c r="AY143" t="inlineStr">
+      <c r="AY144" t="inlineStr">
         <is>
           <t>cube_csv</t>
         </is>
       </c>
-      <c r="AZ143" t="inlineStr">
+      <c r="AZ144" t="inlineStr">
         <is>
           <t>thl_ttr</t>
         </is>
       </c>
-      <c r="BA143" t="inlineStr">
+      <c r="BA144" t="inlineStr">
         <is>
           <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
-      <c r="BB143" t="inlineStr">
+      <c r="BB144" t="inlineStr">
         <is>
           <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
-      <c r="BC143" t="inlineStr">
+      <c r="BC144" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>D165</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>amebiasis</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>Amebiasis</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>FI</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>D165</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>Amebiasis</t>
+        </is>
+      </c>
+      <c r="J145" t="inlineStr">
+        <is>
+          <t>阿米巴病</t>
+        </is>
+      </c>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L145" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="M145" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N145" t="n">
+        <v>0</v>
+      </c>
+      <c r="O145" t="n">
+        <v>0</v>
+      </c>
+      <c r="U145" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1290</t>
+        </is>
+      </c>
+      <c r="V145" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1290</t>
+        </is>
+      </c>
+      <c r="W145" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X145" t="inlineStr">
+        <is>
+          <t>Amebiasis</t>
+        </is>
+      </c>
+      <c r="Y145" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z145" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA145" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB145" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC145" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD145" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE145" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF145" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG145" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH145" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI145" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ145" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK145" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; THL reporting group code 1290.</t>
+        </is>
+      </c>
+      <c r="AM145" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN145" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO145" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP145" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ145" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AS145" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1290</t>
+        </is>
+      </c>
+      <c r="AT145" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU145" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
+      </c>
+      <c r="AV145" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="AW145" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="AX145" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="AY145" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+      <c r="AZ145" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="BA145" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="BB145" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="BC145" t="inlineStr">
         <is>
           <t>cube_csv</t>
         </is>
@@ -28167,7 +28566,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="10">
@@ -28177,7 +28576,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>142</v>
+        <v>144</v>
       </c>
     </row>
     <row r="11">
@@ -28197,7 +28596,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="13">
@@ -28229,7 +28628,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>555</v>
+        <v>559</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d165/2026-2029.xlsx
+++ b/diseases/d165/2026-2029.xlsx
@@ -1556,6 +1556,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO6" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2097,6 +2102,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO9" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4630,6 +4640,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO22" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5573,6 +5588,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO27" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7707,6 +7727,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO38" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8650,6 +8675,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO43" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11186,6 +11216,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO56" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11724,6 +11759,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO59" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13464,10 +13504,10 @@
         </is>
       </c>
       <c r="N68" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O68" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="S68" t="inlineStr">
         <is>
@@ -13620,10 +13660,10 @@
         </is>
       </c>
       <c r="N69" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O69" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U69" t="inlineStr">
         <is>
@@ -14260,6 +14300,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO72" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14798,6 +14843,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO75" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -17736,6 +17786,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA90" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO90" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -18274,6 +18329,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA93" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO93" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -20798,6 +20858,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA106" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO106" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -21336,6 +21401,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA109" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO109" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -23025,12 +23095,12 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>CA-ON</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Ontario, Canada</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -23064,22 +23134,19 @@
         </is>
       </c>
       <c r="N118" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="O118" t="n">
-        <v>1</v>
-      </c>
-      <c r="R118" t="n">
-        <v>0.01778809170864137</v>
+        <v>5</v>
       </c>
       <c r="S118" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>missing_population</t>
         </is>
       </c>
       <c r="U118" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1290</t>
+          <t>SER_CA_ON_PHO_IDTO_AMEBIASIS_MONTHLY</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
@@ -23099,12 +23166,12 @@
       </c>
       <c r="AQ118" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS118" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1290</t>
+          <t>SER_CA_ON_PHO_IDTO_AMEBIASIS_MONTHLY</t>
         </is>
       </c>
       <c r="AT118" t="n">
@@ -23112,47 +23179,47 @@
       </c>
       <c r="AU118" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV118" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ118" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="BA118" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="BB118" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="BC118" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -23184,12 +23251,12 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>CA-ON</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Ontario, Canada</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -23223,24 +23290,24 @@
         </is>
       </c>
       <c r="N119" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="O119" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="U119" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1290</t>
+          <t>SER_CA_ON_PHO_IDTO_AMEBIASIS_MONTHLY</t>
         </is>
       </c>
       <c r="V119" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1290</t>
+          <t>SER_CA_ON_PHO_IDTO_AMEBIASIS_MONTHLY</t>
         </is>
       </c>
       <c r="W119" t="inlineStr">
         <is>
-          <t>SRC_FI_THL_TTR</t>
+          <t>SRC_CA_ON_PHO_IDTO</t>
         </is>
       </c>
       <c r="X119" t="inlineStr">
@@ -23255,7 +23322,7 @@
       </c>
       <c r="Z119" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
@@ -23270,7 +23337,7 @@
       </c>
       <c r="AC119" t="inlineStr">
         <is>
-          <t>country:FI:national</t>
+          <t>country:CA-ON:national</t>
         </is>
       </c>
       <c r="AD119" t="inlineStr">
@@ -23305,17 +23372,17 @@
       </c>
       <c r="AJ119" t="inlineStr">
         <is>
-          <t>FI_THL_TTR_reporting_group</t>
+          <t>PHO_IDTO_2026_07</t>
         </is>
       </c>
       <c r="AK119" t="inlineStr">
         <is>
-          <t>Finland THL national monthly notification series; THL reporting group code 1290.</t>
+          <t>PHO IDTO current-year monthly preliminary amebiasis notifications; confirmed cases only under the July 2026 technical notes.</t>
         </is>
       </c>
       <c r="AM119" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>provisional</t>
         </is>
       </c>
       <c r="AN119" t="b">
@@ -23333,12 +23400,12 @@
       </c>
       <c r="AQ119" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS119" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1290</t>
+          <t>SER_CA_ON_PHO_IDTO_AMEBIASIS_MONTHLY</t>
         </is>
       </c>
       <c r="AT119" t="n">
@@ -23346,47 +23413,47 @@
       </c>
       <c r="AU119" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV119" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="AW119" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="AY119" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ119" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="BA119" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="BB119" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="BC119" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -23418,12 +23485,12 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -23463,75 +23530,89 @@
         <v>1</v>
       </c>
       <c r="R120" t="n">
-        <v>0.01355270280196709</v>
+        <v>0.01778809170864137</v>
       </c>
       <c r="S120" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U120" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1290</t>
+        </is>
+      </c>
+      <c r="AA120" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO120" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP120" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR120" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS120" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ120" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AS120" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1290</t>
+        </is>
+      </c>
       <c r="AT120" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU120" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV120" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW120" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY120" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ120" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA120" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB120" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC120" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -23558,17 +23639,17 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -23607,17 +23688,34 @@
       <c r="O121" t="n">
         <v>1</v>
       </c>
-      <c r="R121" t="n">
-        <v>0.009344880428283346</v>
-      </c>
-      <c r="S121" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U121" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_ENTAMOEBA</t>
+          <t>SER_FI_THL_TTR_1290</t>
+        </is>
+      </c>
+      <c r="V121" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1290</t>
+        </is>
+      </c>
+      <c r="W121" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X121" t="inlineStr">
+        <is>
+          <t>Amebiasis</t>
+        </is>
+      </c>
+      <c r="Y121" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z121" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
@@ -23625,6 +23723,64 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB121" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC121" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD121" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE121" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF121" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG121" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH121" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI121" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ121" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK121" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; THL reporting group code 1290.</t>
+        </is>
+      </c>
+      <c r="AM121" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN121" t="b">
+        <v>1</v>
+      </c>
       <c r="AO121" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -23637,12 +23793,12 @@
       </c>
       <c r="AQ121" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AS121" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_ENTAMOEBA</t>
+          <t>SER_FI_THL_TTR_1290</t>
         </is>
       </c>
       <c r="AT121" t="n">
@@ -23650,47 +23806,47 @@
       </c>
       <c r="AU121" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV121" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW121" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ121" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA121" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB121" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC121" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -23717,17 +23873,17 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
@@ -23766,34 +23922,12 @@
       <c r="O122" t="n">
         <v>1</v>
       </c>
-      <c r="U122" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_ENTAMOEBA</t>
-        </is>
-      </c>
-      <c r="V122" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_ENTAMOEBA</t>
-        </is>
-      </c>
-      <c r="W122" t="inlineStr">
-        <is>
-          <t>SRC_SE_FOHM_SMINET</t>
-        </is>
-      </c>
-      <c r="X122" t="inlineStr">
-        <is>
-          <t>Entamoeba histolytica</t>
-        </is>
-      </c>
-      <c r="Y122" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z122" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
+      <c r="R122" t="n">
+        <v>0.01355270280196709</v>
+      </c>
+      <c r="S122" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
@@ -23801,130 +23935,68 @@
           <t>monthly</t>
         </is>
       </c>
-      <c r="AB122" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC122" t="inlineStr">
-        <is>
-          <t>country:SE:national</t>
-        </is>
-      </c>
-      <c r="AD122" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE122" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF122" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG122" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH122" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI122" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ122" t="inlineStr">
-        <is>
-          <t>SE_FOHM_SMINET_current</t>
-        </is>
-      </c>
-      <c r="AK122" t="inlineStr">
-        <is>
-          <t>Sweden FHM SmiNet national monthly notification series; FHM Entamoeba histolytica source category.</t>
-        </is>
-      </c>
-      <c r="AM122" t="inlineStr">
-        <is>
-          <t>revised</t>
-        </is>
-      </c>
-      <c r="AN122" t="b">
-        <v>1</v>
-      </c>
       <c r="AO122" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP122" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ122" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS122" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_ENTAMOEBA</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR122" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS122" t="inlineStr"/>
       <c r="AT122" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU122" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV122" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW122" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ122" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA122" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB122" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC122" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -23956,12 +24028,12 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Taiwan, China</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
@@ -23995,81 +24067,95 @@
         </is>
       </c>
       <c r="N123" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="O123" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="R123" t="n">
-        <v>0.04345692446436896</v>
+        <v>0.009344880428283346</v>
       </c>
       <c r="S123" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U123" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_ENTAMOEBA</t>
+        </is>
+      </c>
+      <c r="AA123" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO123" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP123" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR123" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS123" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ123" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS123" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_ENTAMOEBA</t>
+        </is>
+      </c>
       <c r="AT123" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU123" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV123" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW123" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY123" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ123" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA123" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB123" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC123" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -24096,17 +24182,17 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
@@ -24131,7 +24217,7 @@
       </c>
       <c r="L124" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M124" t="inlineStr">
@@ -24140,31 +24226,103 @@
         </is>
       </c>
       <c r="N124" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="O124" t="n">
-        <v>9</v>
-      </c>
-      <c r="P124" t="n">
-        <v>9</v>
-      </c>
-      <c r="R124" t="n">
-        <v>0.007351275668091897</v>
-      </c>
-      <c r="S124" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="U124" t="inlineStr">
         <is>
-          <t>SER_JP_AMEBIASIS_WEEKLY</t>
+          <t>SER_SE_FOHM_SMINET_ENTAMOEBA</t>
+        </is>
+      </c>
+      <c r="V124" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_ENTAMOEBA</t>
+        </is>
+      </c>
+      <c r="W124" t="inlineStr">
+        <is>
+          <t>SRC_SE_FOHM_SMINET</t>
+        </is>
+      </c>
+      <c r="X124" t="inlineStr">
+        <is>
+          <t>Entamoeba histolytica</t>
+        </is>
+      </c>
+      <c r="Y124" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z124" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
         <is>
-          <t>weekly</t>
-        </is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB124" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC124" t="inlineStr">
+        <is>
+          <t>country:SE:national</t>
+        </is>
+      </c>
+      <c r="AD124" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE124" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF124" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG124" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH124" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI124" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ124" t="inlineStr">
+        <is>
+          <t>SE_FOHM_SMINET_current</t>
+        </is>
+      </c>
+      <c r="AK124" t="inlineStr">
+        <is>
+          <t>Sweden FHM SmiNet national monthly notification series; FHM Entamoeba histolytica source category.</t>
+        </is>
+      </c>
+      <c r="AM124" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN124" t="b">
+        <v>1</v>
       </c>
       <c r="AO124" t="inlineStr">
         <is>
@@ -24183,7 +24341,7 @@
       </c>
       <c r="AS124" t="inlineStr">
         <is>
-          <t>SER_JP_AMEBIASIS_WEEKLY</t>
+          <t>SER_SE_FOHM_SMINET_ENTAMOEBA</t>
         </is>
       </c>
       <c r="AT124" t="n">
@@ -24196,42 +24354,42 @@
       </c>
       <c r="AV124" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW124" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY124" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ124" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA124" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB124" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC124" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -24258,17 +24416,17 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>TW</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Taiwan, China</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
@@ -24293,7 +24451,7 @@
       </c>
       <c r="L125" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M125" t="inlineStr">
@@ -24302,173 +24460,86 @@
         </is>
       </c>
       <c r="N125" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O125" t="n">
-        <v>9</v>
-      </c>
-      <c r="P125" t="n">
-        <v>9</v>
-      </c>
-      <c r="U125" t="inlineStr">
-        <is>
-          <t>SER_JP_AMEBIASIS_WEEKLY</t>
-        </is>
-      </c>
-      <c r="V125" t="inlineStr">
-        <is>
-          <t>SER_JP_AMEBIASIS_WEEKLY</t>
-        </is>
-      </c>
-      <c r="W125" t="inlineStr">
-        <is>
-          <t>SRC_JP_NIID</t>
-        </is>
-      </c>
-      <c r="X125" t="inlineStr">
-        <is>
-          <t>Amoebic dysentery</t>
-        </is>
-      </c>
-      <c r="Y125" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z125" t="inlineStr">
-        <is>
-          <t>notification</t>
+        <v>10</v>
+      </c>
+      <c r="R125" t="n">
+        <v>0.04345692446436896</v>
+      </c>
+      <c r="S125" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA125" t="inlineStr">
         <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB125" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC125" t="inlineStr">
-        <is>
-          <t>country:JP:national</t>
-        </is>
-      </c>
-      <c r="AD125" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE125" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF125" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG125" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH125" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI125" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ125" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
-        </is>
-      </c>
-      <c r="AK125" t="inlineStr">
-        <is>
-          <t>Japan NIID amoebic dysentery notifications.</t>
-        </is>
-      </c>
-      <c r="AM125" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN125" t="b">
-        <v>1</v>
+          <t>monthly</t>
+        </is>
       </c>
       <c r="AO125" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP125" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ125" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS125" t="inlineStr">
-        <is>
-          <t>SER_JP_AMEBIASIS_WEEKLY</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR125" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS125" t="inlineStr"/>
       <c r="AT125" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU125" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV125" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="AW125" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="AX125" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="AY125" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ125" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="BA125" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="BB125" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="BC125" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -24530,7 +24601,7 @@
       </c>
       <c r="L126" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M126" t="inlineStr">
@@ -24539,16 +24610,16 @@
         </is>
       </c>
       <c r="N126" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="O126" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="P126" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="R126" t="n">
-        <v>0.00653446726052613</v>
+        <v>0.007351275668091897</v>
       </c>
       <c r="S126" t="inlineStr">
         <is>
@@ -24692,7 +24763,7 @@
       </c>
       <c r="L127" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M127" t="inlineStr">
@@ -24701,13 +24772,13 @@
         </is>
       </c>
       <c r="N127" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="O127" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="P127" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U127" t="inlineStr">
         <is>
@@ -24929,7 +25000,7 @@
       </c>
       <c r="L128" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="M128" t="inlineStr">
@@ -24938,16 +25009,16 @@
         </is>
       </c>
       <c r="N128" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="O128" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="P128" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="R128" t="n">
-        <v>0.001633616815131532</v>
+        <v>0.00653446726052613</v>
       </c>
       <c r="S128" t="inlineStr">
         <is>
@@ -25091,7 +25162,7 @@
       </c>
       <c r="L129" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="M129" t="inlineStr">
@@ -25100,13 +25171,13 @@
         </is>
       </c>
       <c r="N129" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="O129" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="P129" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="U129" t="inlineStr">
         <is>
@@ -25328,7 +25399,7 @@
       </c>
       <c r="L130" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="M130" t="inlineStr">
@@ -25337,16 +25408,16 @@
         </is>
       </c>
       <c r="N130" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="O130" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="P130" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="R130" t="n">
-        <v>0.00898489248322343</v>
+        <v>0.001633616815131532</v>
       </c>
       <c r="S130" t="inlineStr">
         <is>
@@ -25490,7 +25561,7 @@
       </c>
       <c r="L131" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="M131" t="inlineStr">
@@ -25499,13 +25570,13 @@
         </is>
       </c>
       <c r="N131" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="O131" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="P131" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="U131" t="inlineStr">
         <is>
@@ -25727,7 +25798,7 @@
       </c>
       <c r="L132" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="M132" t="inlineStr">
@@ -25736,16 +25807,16 @@
         </is>
       </c>
       <c r="N132" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="O132" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="P132" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="R132" t="n">
-        <v>0.0008168084075657662</v>
+        <v>0.00898489248322343</v>
       </c>
       <c r="S132" t="inlineStr">
         <is>
@@ -25889,7 +25960,7 @@
       </c>
       <c r="L133" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="M133" t="inlineStr">
@@ -25898,13 +25969,13 @@
         </is>
       </c>
       <c r="N133" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="O133" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="P133" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="U133" t="inlineStr">
         <is>
@@ -26096,12 +26167,12 @@
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
@@ -26126,22 +26197,25 @@
       </c>
       <c r="L134" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="M134" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N134" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O134" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="P134" t="n">
+        <v>1</v>
       </c>
       <c r="R134" t="n">
-        <v>0</v>
+        <v>0.0008168084075657662</v>
       </c>
       <c r="S134" t="inlineStr">
         <is>
@@ -26150,12 +26224,12 @@
       </c>
       <c r="U134" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1290</t>
+          <t>SER_JP_AMEBIASIS_WEEKLY</t>
         </is>
       </c>
       <c r="AA134" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO134" t="inlineStr">
@@ -26170,12 +26244,12 @@
       </c>
       <c r="AQ134" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS134" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1290</t>
+          <t>SER_JP_AMEBIASIS_WEEKLY</t>
         </is>
       </c>
       <c r="AT134" t="n">
@@ -26183,47 +26257,47 @@
       </c>
       <c r="AU134" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV134" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW134" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX134" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY134" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ134" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA134" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB134" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC134" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -26255,12 +26329,12 @@
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
@@ -26285,38 +26359,41 @@
       </c>
       <c r="L135" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="M135" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N135" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O135" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="P135" t="n">
+        <v>1</v>
       </c>
       <c r="U135" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1290</t>
+          <t>SER_JP_AMEBIASIS_WEEKLY</t>
         </is>
       </c>
       <c r="V135" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1290</t>
+          <t>SER_JP_AMEBIASIS_WEEKLY</t>
         </is>
       </c>
       <c r="W135" t="inlineStr">
         <is>
-          <t>SRC_FI_THL_TTR</t>
+          <t>SRC_JP_NIID</t>
         </is>
       </c>
       <c r="X135" t="inlineStr">
         <is>
-          <t>Amebiasis</t>
+          <t>Amoebic dysentery</t>
         </is>
       </c>
       <c r="Y135" t="inlineStr">
@@ -26326,12 +26403,12 @@
       </c>
       <c r="Z135" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA135" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AB135" t="inlineStr">
@@ -26341,7 +26418,7 @@
       </c>
       <c r="AC135" t="inlineStr">
         <is>
-          <t>country:FI:national</t>
+          <t>country:JP:national</t>
         </is>
       </c>
       <c r="AD135" t="inlineStr">
@@ -26356,7 +26433,7 @@
       </c>
       <c r="AF135" t="inlineStr">
         <is>
-          <t>conditional</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="AG135" t="inlineStr">
@@ -26376,12 +26453,12 @@
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>FI_THL_TTR_reporting_group</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK135" t="inlineStr">
         <is>
-          <t>Finland THL national monthly notification series; THL reporting group code 1290.</t>
+          <t>Japan NIID amoebic dysentery notifications.</t>
         </is>
       </c>
       <c r="AM135" t="inlineStr">
@@ -26404,12 +26481,12 @@
       </c>
       <c r="AQ135" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS135" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1290</t>
+          <t>SER_JP_AMEBIASIS_WEEKLY</t>
         </is>
       </c>
       <c r="AT135" t="n">
@@ -26417,47 +26494,47 @@
       </c>
       <c r="AU135" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV135" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW135" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX135" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY135" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ135" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA135" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB135" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC135" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -26489,12 +26566,12 @@
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
@@ -26519,7 +26596,7 @@
       </c>
       <c r="L136" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="M136" t="inlineStr">
@@ -26528,16 +26605,13 @@
         </is>
       </c>
       <c r="N136" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="O136" t="n">
-        <v>10</v>
-      </c>
-      <c r="P136" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="R136" t="n">
-        <v>0.008168084075657663</v>
+        <v>0</v>
       </c>
       <c r="S136" t="inlineStr">
         <is>
@@ -26546,12 +26620,12 @@
       </c>
       <c r="U136" t="inlineStr">
         <is>
-          <t>SER_JP_AMEBIASIS_WEEKLY</t>
+          <t>SER_FI_THL_TTR_1290</t>
         </is>
       </c>
       <c r="AA136" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO136" t="inlineStr">
@@ -26566,12 +26640,12 @@
       </c>
       <c r="AQ136" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AS136" t="inlineStr">
         <is>
-          <t>SER_JP_AMEBIASIS_WEEKLY</t>
+          <t>SER_FI_THL_TTR_1290</t>
         </is>
       </c>
       <c r="AT136" t="n">
@@ -26579,47 +26653,47 @@
       </c>
       <c r="AU136" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV136" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW136" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX136" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY136" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ136" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA136" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB136" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC136" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -26651,12 +26725,12 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
@@ -26681,7 +26755,7 @@
       </c>
       <c r="L137" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="M137" t="inlineStr">
@@ -26690,32 +26764,29 @@
         </is>
       </c>
       <c r="N137" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="O137" t="n">
-        <v>10</v>
-      </c>
-      <c r="P137" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="U137" t="inlineStr">
         <is>
-          <t>SER_JP_AMEBIASIS_WEEKLY</t>
+          <t>SER_FI_THL_TTR_1290</t>
         </is>
       </c>
       <c r="V137" t="inlineStr">
         <is>
-          <t>SER_JP_AMEBIASIS_WEEKLY</t>
+          <t>SER_FI_THL_TTR_1290</t>
         </is>
       </c>
       <c r="W137" t="inlineStr">
         <is>
-          <t>SRC_JP_NIID</t>
+          <t>SRC_FI_THL_TTR</t>
         </is>
       </c>
       <c r="X137" t="inlineStr">
         <is>
-          <t>Amoebic dysentery</t>
+          <t>Amebiasis</t>
         </is>
       </c>
       <c r="Y137" t="inlineStr">
@@ -26725,12 +26796,12 @@
       </c>
       <c r="Z137" t="inlineStr">
         <is>
-          <t>notification</t>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA137" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AB137" t="inlineStr">
@@ -26740,7 +26811,7 @@
       </c>
       <c r="AC137" t="inlineStr">
         <is>
-          <t>country:JP:national</t>
+          <t>country:FI:national</t>
         </is>
       </c>
       <c r="AD137" t="inlineStr">
@@ -26755,7 +26826,7 @@
       </c>
       <c r="AF137" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>conditional</t>
         </is>
       </c>
       <c r="AG137" t="inlineStr">
@@ -26775,12 +26846,12 @@
       </c>
       <c r="AJ137" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>FI_THL_TTR_reporting_group</t>
         </is>
       </c>
       <c r="AK137" t="inlineStr">
         <is>
-          <t>Japan NIID amoebic dysentery notifications.</t>
+          <t>Finland THL national monthly notification series; THL reporting group code 1290.</t>
         </is>
       </c>
       <c r="AM137" t="inlineStr">
@@ -26803,12 +26874,12 @@
       </c>
       <c r="AQ137" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AS137" t="inlineStr">
         <is>
-          <t>SER_JP_AMEBIASIS_WEEKLY</t>
+          <t>SER_FI_THL_TTR_1290</t>
         </is>
       </c>
       <c r="AT137" t="n">
@@ -26816,47 +26887,47 @@
       </c>
       <c r="AU137" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV137" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW137" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX137" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY137" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ137" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA137" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB137" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC137" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -26888,12 +26959,12 @@
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
@@ -26918,7 +26989,7 @@
       </c>
       <c r="L138" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="M138" t="inlineStr">
@@ -26927,16 +26998,13 @@
         </is>
       </c>
       <c r="N138" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="O138" t="n">
-        <v>10</v>
-      </c>
-      <c r="P138" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="R138" t="n">
-        <v>0.008168084075657663</v>
+        <v>0.02803464128485004</v>
       </c>
       <c r="S138" t="inlineStr">
         <is>
@@ -26945,12 +27013,12 @@
       </c>
       <c r="U138" t="inlineStr">
         <is>
-          <t>SER_JP_AMEBIASIS_WEEKLY</t>
+          <t>SER_SE_FOHM_SMINET_ENTAMOEBA</t>
         </is>
       </c>
       <c r="AA138" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO138" t="inlineStr">
@@ -26970,7 +27038,7 @@
       </c>
       <c r="AS138" t="inlineStr">
         <is>
-          <t>SER_JP_AMEBIASIS_WEEKLY</t>
+          <t>SER_SE_FOHM_SMINET_ENTAMOEBA</t>
         </is>
       </c>
       <c r="AT138" t="n">
@@ -26983,42 +27051,42 @@
       </c>
       <c r="AV138" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW138" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX138" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY138" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ138" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA138" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB138" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC138" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -27050,12 +27118,12 @@
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
@@ -27080,7 +27148,7 @@
       </c>
       <c r="L139" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="M139" t="inlineStr">
@@ -27089,32 +27157,29 @@
         </is>
       </c>
       <c r="N139" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="O139" t="n">
-        <v>10</v>
-      </c>
-      <c r="P139" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="U139" t="inlineStr">
         <is>
-          <t>SER_JP_AMEBIASIS_WEEKLY</t>
+          <t>SER_SE_FOHM_SMINET_ENTAMOEBA</t>
         </is>
       </c>
       <c r="V139" t="inlineStr">
         <is>
-          <t>SER_JP_AMEBIASIS_WEEKLY</t>
+          <t>SER_SE_FOHM_SMINET_ENTAMOEBA</t>
         </is>
       </c>
       <c r="W139" t="inlineStr">
         <is>
-          <t>SRC_JP_NIID</t>
+          <t>SRC_SE_FOHM_SMINET</t>
         </is>
       </c>
       <c r="X139" t="inlineStr">
         <is>
-          <t>Amoebic dysentery</t>
+          <t>Entamoeba histolytica</t>
         </is>
       </c>
       <c r="Y139" t="inlineStr">
@@ -27124,12 +27189,12 @@
       </c>
       <c r="Z139" t="inlineStr">
         <is>
-          <t>notification</t>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA139" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AB139" t="inlineStr">
@@ -27139,7 +27204,7 @@
       </c>
       <c r="AC139" t="inlineStr">
         <is>
-          <t>country:JP:national</t>
+          <t>country:SE:national</t>
         </is>
       </c>
       <c r="AD139" t="inlineStr">
@@ -27154,7 +27219,7 @@
       </c>
       <c r="AF139" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>conditional</t>
         </is>
       </c>
       <c r="AG139" t="inlineStr">
@@ -27174,17 +27239,17 @@
       </c>
       <c r="AJ139" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>SE_FOHM_SMINET_current</t>
         </is>
       </c>
       <c r="AK139" t="inlineStr">
         <is>
-          <t>Japan NIID amoebic dysentery notifications.</t>
+          <t>Sweden FHM SmiNet national monthly notification series; FHM Entamoeba histolytica source category.</t>
         </is>
       </c>
       <c r="AM139" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>revised</t>
         </is>
       </c>
       <c r="AN139" t="b">
@@ -27207,7 +27272,7 @@
       </c>
       <c r="AS139" t="inlineStr">
         <is>
-          <t>SER_JP_AMEBIASIS_WEEKLY</t>
+          <t>SER_SE_FOHM_SMINET_ENTAMOEBA</t>
         </is>
       </c>
       <c r="AT139" t="n">
@@ -27220,42 +27285,42 @@
       </c>
       <c r="AV139" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW139" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX139" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY139" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ139" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA139" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB139" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC139" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -27317,7 +27382,7 @@
       </c>
       <c r="L140" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="M140" t="inlineStr">
@@ -27326,16 +27391,16 @@
         </is>
       </c>
       <c r="N140" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O140" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="P140" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="R140" t="n">
-        <v>0.007351275668091897</v>
+        <v>0.008168084075657663</v>
       </c>
       <c r="S140" t="inlineStr">
         <is>
@@ -27479,7 +27544,7 @@
       </c>
       <c r="L141" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="M141" t="inlineStr">
@@ -27488,13 +27553,13 @@
         </is>
       </c>
       <c r="N141" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O141" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="P141" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U141" t="inlineStr">
         <is>
@@ -27716,7 +27781,7 @@
       </c>
       <c r="L142" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="M142" t="inlineStr">
@@ -27725,16 +27790,16 @@
         </is>
       </c>
       <c r="N142" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="O142" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="P142" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="R142" t="n">
-        <v>0.003267233630263065</v>
+        <v>0.008168084075657663</v>
       </c>
       <c r="S142" t="inlineStr">
         <is>
@@ -27878,7 +27943,7 @@
       </c>
       <c r="L143" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="M143" t="inlineStr">
@@ -27887,13 +27952,13 @@
         </is>
       </c>
       <c r="N143" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="O143" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="P143" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="U143" t="inlineStr">
         <is>
@@ -28085,12 +28150,12 @@
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
@@ -28115,22 +28180,25 @@
       </c>
       <c r="L144" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="M144" t="inlineStr">
         <is>
-          <t>2026-10</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="N144" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="O144" t="n">
-        <v>0</v>
+        <v>9</v>
+      </c>
+      <c r="P144" t="n">
+        <v>9</v>
       </c>
       <c r="R144" t="n">
-        <v>0</v>
+        <v>0.007351275668091897</v>
       </c>
       <c r="S144" t="inlineStr">
         <is>
@@ -28139,12 +28207,12 @@
       </c>
       <c r="U144" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1290</t>
+          <t>SER_JP_AMEBIASIS_WEEKLY</t>
         </is>
       </c>
       <c r="AA144" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO144" t="inlineStr">
@@ -28159,12 +28227,12 @@
       </c>
       <c r="AQ144" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS144" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1290</t>
+          <t>SER_JP_AMEBIASIS_WEEKLY</t>
         </is>
       </c>
       <c r="AT144" t="n">
@@ -28172,47 +28240,47 @@
       </c>
       <c r="AU144" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV144" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW144" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX144" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY144" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ144" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA144" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB144" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC144" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -28244,12 +28312,12 @@
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
@@ -28274,38 +28342,41 @@
       </c>
       <c r="L145" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="M145" t="inlineStr">
         <is>
-          <t>2026-10</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="N145" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="O145" t="n">
-        <v>0</v>
+        <v>9</v>
+      </c>
+      <c r="P145" t="n">
+        <v>9</v>
       </c>
       <c r="U145" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1290</t>
+          <t>SER_JP_AMEBIASIS_WEEKLY</t>
         </is>
       </c>
       <c r="V145" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1290</t>
+          <t>SER_JP_AMEBIASIS_WEEKLY</t>
         </is>
       </c>
       <c r="W145" t="inlineStr">
         <is>
-          <t>SRC_FI_THL_TTR</t>
+          <t>SRC_JP_NIID</t>
         </is>
       </c>
       <c r="X145" t="inlineStr">
         <is>
-          <t>Amebiasis</t>
+          <t>Amoebic dysentery</t>
         </is>
       </c>
       <c r="Y145" t="inlineStr">
@@ -28315,12 +28386,12 @@
       </c>
       <c r="Z145" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA145" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AB145" t="inlineStr">
@@ -28330,7 +28401,7 @@
       </c>
       <c r="AC145" t="inlineStr">
         <is>
-          <t>country:FI:national</t>
+          <t>country:JP:national</t>
         </is>
       </c>
       <c r="AD145" t="inlineStr">
@@ -28345,7 +28416,7 @@
       </c>
       <c r="AF145" t="inlineStr">
         <is>
-          <t>conditional</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="AG145" t="inlineStr">
@@ -28365,12 +28436,12 @@
       </c>
       <c r="AJ145" t="inlineStr">
         <is>
-          <t>FI_THL_TTR_reporting_group</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK145" t="inlineStr">
         <is>
-          <t>Finland THL national monthly notification series; THL reporting group code 1290.</t>
+          <t>Japan NIID amoebic dysentery notifications.</t>
         </is>
       </c>
       <c r="AM145" t="inlineStr">
@@ -28393,12 +28464,12 @@
       </c>
       <c r="AQ145" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS145" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1290</t>
+          <t>SER_JP_AMEBIASIS_WEEKLY</t>
         </is>
       </c>
       <c r="AT145" t="n">
@@ -28406,45 +28477,837 @@
       </c>
       <c r="AU145" t="inlineStr">
         <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV145" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW145" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX145" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY145" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ145" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA145" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB145" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC145" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>D165</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>amebiasis</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>Amebiasis</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>D165</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>Amebiasis</t>
+        </is>
+      </c>
+      <c r="J146" t="inlineStr">
+        <is>
+          <t>阿米巴病</t>
+        </is>
+      </c>
+      <c r="K146" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L146" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="M146" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N146" t="n">
+        <v>4</v>
+      </c>
+      <c r="O146" t="n">
+        <v>4</v>
+      </c>
+      <c r="P146" t="n">
+        <v>4</v>
+      </c>
+      <c r="R146" t="n">
+        <v>0.003267233630263065</v>
+      </c>
+      <c r="S146" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U146" t="inlineStr">
+        <is>
+          <t>SER_JP_AMEBIASIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AA146" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO146" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP146" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ146" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS146" t="inlineStr">
+        <is>
+          <t>SER_JP_AMEBIASIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT146" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU146" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV146" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW146" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX146" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY146" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ146" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA146" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB146" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC146" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>D165</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>amebiasis</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>Amebiasis</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>D165</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>Amebiasis</t>
+        </is>
+      </c>
+      <c r="J147" t="inlineStr">
+        <is>
+          <t>阿米巴病</t>
+        </is>
+      </c>
+      <c r="K147" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L147" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="M147" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N147" t="n">
+        <v>4</v>
+      </c>
+      <c r="O147" t="n">
+        <v>4</v>
+      </c>
+      <c r="P147" t="n">
+        <v>4</v>
+      </c>
+      <c r="U147" t="inlineStr">
+        <is>
+          <t>SER_JP_AMEBIASIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V147" t="inlineStr">
+        <is>
+          <t>SER_JP_AMEBIASIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W147" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X147" t="inlineStr">
+        <is>
+          <t>Amoebic dysentery</t>
+        </is>
+      </c>
+      <c r="Y147" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z147" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA147" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB147" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC147" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD147" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE147" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF147" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG147" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH147" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI147" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ147" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
+        </is>
+      </c>
+      <c r="AK147" t="inlineStr">
+        <is>
+          <t>Japan NIID amoebic dysentery notifications.</t>
+        </is>
+      </c>
+      <c r="AM147" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN147" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO147" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP147" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ147" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS147" t="inlineStr">
+        <is>
+          <t>SER_JP_AMEBIASIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT147" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU147" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV147" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW147" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX147" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY147" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ147" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA147" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB147" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC147" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>D165</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>amebiasis</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>Amebiasis</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>FI</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>D165</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>Amebiasis</t>
+        </is>
+      </c>
+      <c r="J148" t="inlineStr">
+        <is>
+          <t>阿米巴病</t>
+        </is>
+      </c>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L148" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="M148" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N148" t="n">
+        <v>0</v>
+      </c>
+      <c r="O148" t="n">
+        <v>0</v>
+      </c>
+      <c r="R148" t="n">
+        <v>0</v>
+      </c>
+      <c r="S148" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U148" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1290</t>
+        </is>
+      </c>
+      <c r="AA148" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO148" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP148" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ148" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AS148" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1290</t>
+        </is>
+      </c>
+      <c r="AT148" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU148" t="inlineStr">
+        <is>
           <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
-      <c r="AV145" t="inlineStr">
+      <c r="AV148" t="inlineStr">
         <is>
           <t>thl_ttr</t>
         </is>
       </c>
-      <c r="AW145" t="inlineStr">
+      <c r="AW148" t="inlineStr">
         <is>
           <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
-      <c r="AX145" t="inlineStr">
+      <c r="AX148" t="inlineStr">
         <is>
           <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
-      <c r="AY145" t="inlineStr">
+      <c r="AY148" t="inlineStr">
         <is>
           <t>cube_csv</t>
         </is>
       </c>
-      <c r="AZ145" t="inlineStr">
+      <c r="AZ148" t="inlineStr">
         <is>
           <t>thl_ttr</t>
         </is>
       </c>
-      <c r="BA145" t="inlineStr">
+      <c r="BA148" t="inlineStr">
         <is>
           <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
-      <c r="BB145" t="inlineStr">
+      <c r="BB148" t="inlineStr">
         <is>
           <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
-      <c r="BC145" t="inlineStr">
+      <c r="BC148" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>D165</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>amebiasis</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>Amebiasis</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>FI</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>D165</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>Amebiasis</t>
+        </is>
+      </c>
+      <c r="J149" t="inlineStr">
+        <is>
+          <t>阿米巴病</t>
+        </is>
+      </c>
+      <c r="K149" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L149" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="M149" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N149" t="n">
+        <v>0</v>
+      </c>
+      <c r="O149" t="n">
+        <v>0</v>
+      </c>
+      <c r="U149" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1290</t>
+        </is>
+      </c>
+      <c r="V149" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1290</t>
+        </is>
+      </c>
+      <c r="W149" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X149" t="inlineStr">
+        <is>
+          <t>Amebiasis</t>
+        </is>
+      </c>
+      <c r="Y149" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z149" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA149" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB149" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC149" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD149" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE149" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF149" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG149" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH149" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI149" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ149" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK149" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; THL reporting group code 1290.</t>
+        </is>
+      </c>
+      <c r="AM149" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN149" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO149" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP149" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ149" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AS149" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1290</t>
+        </is>
+      </c>
+      <c r="AT149" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU149" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
+      </c>
+      <c r="AV149" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="AW149" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="AX149" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="AY149" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+      <c r="AZ149" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="BA149" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="BB149" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="BC149" t="inlineStr">
         <is>
           <t>cube_csv</t>
         </is>
@@ -28566,7 +29429,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
     </row>
     <row r="10">
@@ -28576,7 +29439,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>144</v>
+        <v>148</v>
       </c>
     </row>
     <row r="11">
@@ -28596,7 +29459,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
     </row>
     <row r="13">
@@ -28628,7 +29491,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>559</v>
+        <v>566</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d165/2026-2029.xlsx
+++ b/diseases/d165/2026-2029.xlsx
@@ -29313,6 +29313,405 @@
         </is>
       </c>
     </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>D165</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>amebiasis</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>Amebiasis</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>D165</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>Amebiasis</t>
+        </is>
+      </c>
+      <c r="J150" t="inlineStr">
+        <is>
+          <t>阿米巴病</t>
+        </is>
+      </c>
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L150" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="M150" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N150" t="n">
+        <v>6</v>
+      </c>
+      <c r="O150" t="n">
+        <v>6</v>
+      </c>
+      <c r="P150" t="n">
+        <v>6</v>
+      </c>
+      <c r="R150" t="n">
+        <v>0.004900850445394598</v>
+      </c>
+      <c r="S150" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U150" t="inlineStr">
+        <is>
+          <t>SER_JP_AMEBIASIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AA150" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO150" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP150" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ150" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS150" t="inlineStr">
+        <is>
+          <t>SER_JP_AMEBIASIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT150" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU150" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV150" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW150" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX150" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY150" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ150" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA150" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB150" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC150" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>D165</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>amebiasis</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>Amebiasis</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>D165</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>Amebiasis</t>
+        </is>
+      </c>
+      <c r="J151" t="inlineStr">
+        <is>
+          <t>阿米巴病</t>
+        </is>
+      </c>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L151" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="M151" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N151" t="n">
+        <v>6</v>
+      </c>
+      <c r="O151" t="n">
+        <v>6</v>
+      </c>
+      <c r="P151" t="n">
+        <v>6</v>
+      </c>
+      <c r="U151" t="inlineStr">
+        <is>
+          <t>SER_JP_AMEBIASIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V151" t="inlineStr">
+        <is>
+          <t>SER_JP_AMEBIASIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W151" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X151" t="inlineStr">
+        <is>
+          <t>Amoebic dysentery</t>
+        </is>
+      </c>
+      <c r="Y151" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z151" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA151" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB151" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC151" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD151" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE151" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF151" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG151" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH151" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI151" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ151" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
+        </is>
+      </c>
+      <c r="AK151" t="inlineStr">
+        <is>
+          <t>Japan NIID amoebic dysentery notifications.</t>
+        </is>
+      </c>
+      <c r="AM151" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN151" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO151" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP151" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ151" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS151" t="inlineStr">
+        <is>
+          <t>SER_JP_AMEBIASIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT151" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU151" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV151" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW151" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX151" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY151" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ151" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA151" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB151" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC151" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -29346,7 +29745,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -29429,7 +29828,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="10">
@@ -29439,7 +29838,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>148</v>
+        <v>150</v>
       </c>
     </row>
     <row r="11">
@@ -29459,7 +29858,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="13">
@@ -29491,7 +29890,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>566</v>
+        <v>572</v>
       </c>
     </row>
     <row r="16">
